--- a/Deliverables/SM_Top Board/_BOM/SM_Top_PCB_LCSC.xlsx
+++ b/Deliverables/SM_Top Board/_BOM/SM_Top_PCB_LCSC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4D011A-C39B-492F-909C-166B54BCC6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4060B9E-6605-424E-A422-D3FAD764FA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -729,9 +729,6 @@
     <t>Texas Instruments</t>
   </si>
   <si>
-    <t>Farnell</t>
-  </si>
-  <si>
     <t>DIODES INC.</t>
   </si>
   <si>
@@ -994,6 +991,9 @@
   </si>
   <si>
     <t>Unable to find chinese supplier. Farnell has 11 parts in stock</t>
+  </si>
+  <si>
+    <t>Local Supplier</t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1303,16 @@
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="5" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1315,7 +1324,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1325,15 +1334,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1640,27 +1640,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="31"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -1685,7 +1685,7 @@
         <v>210</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>211</v>
@@ -1694,7 +1694,7 @@
         <v>212</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>213</v>
@@ -1718,14 +1718,14 @@
         <v>219</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="35" t="s">
         <v>220</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -1741,10 +1741,10 @@
         <v>6</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I3" s="20"/>
       <c r="J3" s="9" t="s">
@@ -1761,7 +1761,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O3" s="11">
         <v>0.24909999999999999</v>
@@ -1784,7 +1784,7 @@
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="9" t="s">
         <v>8</v>
       </c>
@@ -1798,10 +1798,10 @@
         <v>11</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I4" s="21"/>
       <c r="J4" s="9" t="s">
@@ -1818,7 +1818,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O4" s="11">
         <v>4.0000000000000001E-3</v>
@@ -1841,7 +1841,7 @@
         <f t="shared" ref="A5:A56" si="1">A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="9" t="s">
         <v>13</v>
       </c>
@@ -1855,13 +1855,13 @@
         <v>16</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H5" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="I5" s="21" t="s">
         <v>269</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>270</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>12</v>
@@ -1877,7 +1877,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O5" s="11">
         <v>9.8400000000000001E-2</v>
@@ -1894,7 +1894,7 @@
         <v>0.49199999999999999</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B6" s="28"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
@@ -1916,10 +1916,10 @@
         <v>20</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I6" s="20"/>
       <c r="J6" s="9" t="s">
@@ -1936,7 +1936,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O6" s="11">
         <v>0.4869</v>
@@ -1949,7 +1949,7 @@
         <v>0.4869</v>
       </c>
       <c r="R6" s="12">
-        <f t="shared" ref="R6:R55" si="2">Q6*M6</f>
+        <f t="shared" ref="R6:R54" si="2">Q6*M6</f>
         <v>2.4344999999999999</v>
       </c>
       <c r="S6" s="5"/>
@@ -1959,7 +1959,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="9" t="s">
         <v>22</v>
       </c>
@@ -1973,10 +1973,10 @@
         <v>24</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I7" s="20"/>
       <c r="J7" s="9" t="s">
@@ -1993,7 +1993,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O7" s="11">
         <v>7.1099999999999997E-2</v>
@@ -2016,7 +2016,7 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B8" s="28"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="9" t="s">
         <v>26</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>230</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I8" s="20"/>
       <c r="J8" s="9" t="s">
@@ -2050,7 +2050,7 @@
         <v>5</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O8" s="11">
         <v>5.3E-3</v>
@@ -2073,7 +2073,7 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="9" t="s">
         <v>30</v>
       </c>
@@ -2087,10 +2087,10 @@
         <v>33</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I9" s="21"/>
       <c r="J9" s="9" t="s">
@@ -2107,7 +2107,7 @@
         <v>5</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O9" s="11">
         <v>3.27E-2</v>
@@ -2130,7 +2130,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="9" t="s">
         <v>35</v>
       </c>
@@ -2144,10 +2144,10 @@
         <v>37</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I10" s="21"/>
       <c r="J10" s="9" t="s">
@@ -2164,7 +2164,7 @@
         <v>5</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O10" s="11">
         <v>0.30170000000000002</v>
@@ -2187,7 +2187,7 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="9" t="s">
         <v>38</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>230</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="9" t="s">
@@ -2221,13 +2221,13 @@
         <v>5</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O11" s="11">
         <v>1.2200000000000001E-2</v>
       </c>
       <c r="P11" s="12">
-        <f>O11*K11</f>
+        <f t="shared" ref="P11:P16" si="4">O11*K11</f>
         <v>0.61</v>
       </c>
       <c r="Q11" s="11">
@@ -2244,7 +2244,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B12" s="28"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="9" t="s">
         <v>42</v>
       </c>
@@ -2258,10 +2258,10 @@
         <v>44</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I12" s="21"/>
       <c r="J12" s="9" t="s">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O12" s="11">
         <v>3.9300000000000002E-2</v>
       </c>
       <c r="P12" s="12">
-        <f>O12*K12</f>
+        <f t="shared" si="4"/>
         <v>0.39300000000000002</v>
       </c>
       <c r="Q12" s="11">
@@ -2301,7 +2301,7 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B13" s="28"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="9" t="s">
         <v>46</v>
       </c>
@@ -2315,10 +2315,10 @@
         <v>48</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I13" s="21"/>
       <c r="J13" s="9" t="s">
@@ -2335,13 +2335,13 @@
         <v>10</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O13" s="11">
         <v>2.5899999999999999E-2</v>
       </c>
       <c r="P13" s="12">
-        <f>O13*K13</f>
+        <f t="shared" si="4"/>
         <v>0.51800000000000002</v>
       </c>
       <c r="Q13" s="11">
@@ -2358,7 +2358,7 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B14" s="28"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="9" t="s">
         <v>49</v>
       </c>
@@ -2372,10 +2372,10 @@
         <v>51</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="9" t="s">
@@ -2392,13 +2392,13 @@
         <v>10</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O14" s="11">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="P14" s="12">
-        <f>O14*K14</f>
+        <f t="shared" si="4"/>
         <v>0.375</v>
       </c>
       <c r="Q14" s="11">
@@ -2415,27 +2415,27 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B15" s="28"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H15" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>52</v>
@@ -2451,13 +2451,13 @@
         <v>20</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O15" s="11">
         <v>1.9300000000000001E-2</v>
       </c>
       <c r="P15" s="12">
-        <f>O15*K15</f>
+        <f t="shared" si="4"/>
         <v>0.38600000000000001</v>
       </c>
       <c r="Q15" s="11">
@@ -2474,24 +2474,24 @@
         <f>A15+1</f>
         <v>14</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="2" t="s">
@@ -2508,13 +2508,13 @@
         <v>20</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O16" s="4">
         <v>4.9399999999999999E-2</v>
       </c>
       <c r="P16" s="12">
-        <f>O16*K16</f>
+        <f t="shared" si="4"/>
         <v>0.49399999999999999</v>
       </c>
       <c r="Q16" s="4">
@@ -2531,7 +2531,7 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B17" s="28"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="9" t="s">
         <v>54</v>
       </c>
@@ -2545,10 +2545,10 @@
         <v>56</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I17" s="20"/>
       <c r="J17" s="9" t="s">
@@ -2565,7 +2565,7 @@
         <v>5</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O17" s="11">
         <v>0.1</v>
@@ -2588,7 +2588,7 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B18" s="28"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="9" t="s">
         <v>30</v>
       </c>
@@ -2602,10 +2602,10 @@
         <v>33</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I18" s="20"/>
       <c r="J18" s="9" t="s">
@@ -2622,7 +2622,7 @@
         <v>5</v>
       </c>
       <c r="N18" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O18" s="11">
         <v>3.27E-2</v>
@@ -2631,7 +2631,7 @@
         <f>O18*K18</f>
         <v>0.65400000000000003</v>
       </c>
-      <c r="Q18" s="38">
+      <c r="Q18" s="31">
         <v>3.27E-2</v>
       </c>
       <c r="R18" s="12">
@@ -2645,7 +2645,7 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="36" t="s">
         <v>221</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -2661,10 +2661,10 @@
         <v>63</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I19" s="22"/>
       <c r="J19" s="9" t="s">
@@ -2681,7 +2681,7 @@
         <v>20</v>
       </c>
       <c r="N19" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O19" s="11">
         <v>4.7000000000000002E-3</v>
@@ -2704,7 +2704,7 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B20" s="34"/>
+      <c r="B20" s="37"/>
       <c r="C20" s="9" t="s">
         <v>65</v>
       </c>
@@ -2718,10 +2718,10 @@
         <v>64</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I20" s="22"/>
       <c r="J20" s="9" t="s">
@@ -2738,7 +2738,7 @@
         <v>5</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O20" s="4">
         <v>0.66</v>
@@ -2761,7 +2761,7 @@
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B21" s="34"/>
+      <c r="B21" s="37"/>
       <c r="C21" s="9" t="s">
         <v>68</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>67</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="22"/>
@@ -2793,7 +2793,7 @@
         <v>40</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O21" s="4">
         <v>0.36</v>
@@ -2816,7 +2816,7 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B22" s="34"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="9" t="s">
         <v>90</v>
       </c>
@@ -2830,10 +2830,10 @@
         <v>89</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I22" s="22"/>
       <c r="J22" s="9" t="s">
@@ -2850,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O22" s="11">
         <v>0.14299999999999999</v>
@@ -2873,7 +2873,7 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B23" s="35"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="9" t="s">
         <v>93</v>
       </c>
@@ -2887,13 +2887,13 @@
         <v>92</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>92</v>
@@ -2909,7 +2909,7 @@
         <v>5</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O23" s="4">
         <v>7.5800000000000006E-2</v>
@@ -2926,7 +2926,7 @@
         <v>0.75800000000000001</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -2950,10 +2950,10 @@
         <v>71</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9" t="s">
@@ -2970,7 +2970,7 @@
         <v>5</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O24" s="4">
         <v>0.14899999999999999</v>
@@ -3009,10 +3009,10 @@
         <v>86</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9" t="s">
@@ -3029,7 +3029,7 @@
         <v>5</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O25" s="4">
         <v>0.79710000000000003</v>
@@ -3068,10 +3068,10 @@
         <v>108</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9" t="s">
@@ -3088,7 +3088,7 @@
         <v>40</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O26" s="4">
         <v>2.4777</v>
@@ -3111,7 +3111,7 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="36" t="s">
         <v>225</v>
       </c>
       <c r="C27" s="9" t="s">
@@ -3127,10 +3127,10 @@
         <v>115</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9" t="s">
@@ -3147,7 +3147,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O27" s="4">
         <v>1.6999999999999999E-3</v>
@@ -3170,7 +3170,7 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B28" s="34"/>
+      <c r="B28" s="37"/>
       <c r="C28" s="9" t="s">
         <v>117</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>230</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
@@ -3204,7 +3204,7 @@
         <v>10</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O28" s="4">
         <v>1.6999999999999999E-3</v>
@@ -3227,7 +3227,7 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="37"/>
       <c r="C29" s="9" t="s">
         <v>121</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>230</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9" t="s">
@@ -3261,7 +3261,7 @@
         <v>5</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O29" s="4">
         <v>2.0999999999999999E-3</v>
@@ -3284,7 +3284,7 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="37"/>
       <c r="C30" s="9" t="s">
         <v>125</v>
       </c>
@@ -3301,7 +3301,7 @@
         <v>230</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9" t="s">
@@ -3318,20 +3318,20 @@
         <v>5</v>
       </c>
       <c r="N30" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O30" s="11">
         <v>1.4E-3</v>
       </c>
       <c r="P30" s="12">
-        <f t="shared" ref="P30:P32" si="4">O30*K30</f>
+        <f t="shared" ref="P30:P31" si="5">O30*K30</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="Q30" s="11">
         <v>1.4E-3</v>
       </c>
       <c r="R30" s="12">
-        <f t="shared" ref="R30:R32" si="5">Q30*K30</f>
+        <f t="shared" ref="R30:R31" si="6">Q30*K30</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="S30" s="5"/>
@@ -3341,7 +3341,7 @@
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="37"/>
       <c r="C31" s="9" t="s">
         <v>129</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>230</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="9" t="s">
@@ -3375,20 +3375,20 @@
         <v>20</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O31" s="11">
         <v>2.3E-3</v>
       </c>
       <c r="P31" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="Q31" s="11">
         <v>2.3E-3</v>
       </c>
       <c r="R31" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="S31" s="5"/>
@@ -3398,7 +3398,7 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="9" t="s">
         <v>133</v>
       </c>
@@ -3414,8 +3414,8 @@
       <c r="G32" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="H32" s="36" t="s">
-        <v>301</v>
+      <c r="H32" s="29" t="s">
+        <v>300</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="9" t="s">
@@ -3431,14 +3431,14 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N32" s="37" t="s">
-        <v>263</v>
+      <c r="N32" s="30" t="s">
+        <v>262</v>
       </c>
       <c r="O32" s="11">
         <v>8.5699999999999998E-2</v>
       </c>
       <c r="P32" s="12">
-        <f>O32*K32</f>
+        <f t="shared" ref="P32:P40" si="7">O32*K32</f>
         <v>0.42849999999999999</v>
       </c>
       <c r="Q32" s="11">
@@ -3455,7 +3455,7 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="9" t="s">
         <v>138</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>230</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="9" t="s">
@@ -3489,20 +3489,20 @@
         <v>40</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O33" s="11">
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="P33" s="12">
-        <f>O33*K33</f>
+        <f t="shared" si="7"/>
         <v>0.22</v>
       </c>
       <c r="Q33" s="11">
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="R33" s="12">
-        <f>Q33*K33</f>
+        <f t="shared" ref="R33:R40" si="8">Q33*K33</f>
         <v>0.22</v>
       </c>
       <c r="S33" s="5"/>
@@ -3512,7 +3512,7 @@
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="9" t="s">
         <v>142</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>231</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="9" t="s">
@@ -3546,20 +3546,20 @@
         <v>5</v>
       </c>
       <c r="N34" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O34" s="11">
         <v>9.2999999999999992E-3</v>
       </c>
       <c r="P34" s="12">
-        <f>O34*K34</f>
+        <f t="shared" si="7"/>
         <v>0.46499999999999997</v>
       </c>
       <c r="Q34" s="11">
         <v>9.2999999999999992E-3</v>
       </c>
       <c r="R34" s="12">
-        <f>Q34*K34</f>
+        <f t="shared" si="8"/>
         <v>0.46499999999999997</v>
       </c>
       <c r="S34" s="5"/>
@@ -3569,7 +3569,7 @@
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="9" t="s">
         <v>146</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>230</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="9" t="s">
@@ -3603,20 +3603,20 @@
         <v>5</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O35" s="11">
         <v>2E-3</v>
       </c>
       <c r="P35" s="12">
-        <f>O35*K35</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="Q35" s="11">
         <v>2E-3</v>
       </c>
       <c r="R35" s="12">
-        <f>Q35*K35</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="S35" s="5"/>
@@ -3626,7 +3626,7 @@
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="9" t="s">
         <v>150</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>231</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="9" t="s">
@@ -3660,20 +3660,20 @@
         <v>5</v>
       </c>
       <c r="N36" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O36" s="11">
         <v>5.7999999999999996E-3</v>
       </c>
       <c r="P36" s="12">
-        <f>O36*K36</f>
+        <f t="shared" si="7"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Q36" s="11">
         <v>5.7999999999999996E-3</v>
       </c>
       <c r="R36" s="12">
-        <f>Q36*K36</f>
+        <f t="shared" si="8"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="S36" s="5"/>
@@ -3683,7 +3683,7 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B37" s="34"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="9" t="s">
         <v>154</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>230</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="9" t="s">
@@ -3717,20 +3717,20 @@
         <v>5</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O37" s="11">
         <v>2.0999999999999999E-3</v>
       </c>
       <c r="P37" s="12">
-        <f>O37*K37</f>
+        <f t="shared" si="7"/>
         <v>0.21</v>
       </c>
       <c r="Q37" s="11">
         <v>2.0999999999999999E-3</v>
       </c>
       <c r="R37" s="12">
-        <f>Q37*K37</f>
+        <f t="shared" si="8"/>
         <v>0.21</v>
       </c>
       <c r="S37" s="5"/>
@@ -3740,7 +3740,7 @@
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B38" s="34"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="9" t="s">
         <v>158</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>231</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="9" t="s">
@@ -3774,20 +3774,20 @@
         <v>5</v>
       </c>
       <c r="N38" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O38" s="11">
         <v>9.2999999999999992E-3</v>
       </c>
       <c r="P38" s="12">
-        <f>O38*K38</f>
+        <f t="shared" si="7"/>
         <v>0.92999999999999994</v>
       </c>
       <c r="Q38" s="11">
         <v>9.2999999999999992E-3</v>
       </c>
       <c r="R38" s="12">
-        <f>Q38*K38</f>
+        <f t="shared" si="8"/>
         <v>0.92999999999999994</v>
       </c>
       <c r="S38" s="5"/>
@@ -3797,7 +3797,7 @@
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B39" s="34"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="9" t="s">
         <v>162</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>230</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="9" t="s">
@@ -3831,20 +3831,20 @@
         <v>5</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O39" s="11">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="P39" s="12">
-        <f>O39*K39</f>
+        <f t="shared" si="7"/>
         <v>0.26</v>
       </c>
       <c r="Q39" s="11">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="R39" s="12">
-        <f>Q39*K39</f>
+        <f t="shared" si="8"/>
         <v>0.26</v>
       </c>
       <c r="S39" s="5"/>
@@ -3854,7 +3854,7 @@
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B40" s="35"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="9" t="s">
         <v>166</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>230</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="9" t="s">
@@ -3888,20 +3888,20 @@
         <v>5</v>
       </c>
       <c r="N40" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O40" s="11">
         <v>2E-3</v>
       </c>
       <c r="P40" s="12">
-        <f>O40*K40</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="Q40" s="11">
         <v>2E-3</v>
       </c>
       <c r="R40" s="12">
-        <f>Q40*K40</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="S40" s="5"/>
@@ -3911,7 +3911,7 @@
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="36" t="s">
         <v>226</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -3965,7 +3965,7 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="B42" s="35"/>
+      <c r="B42" s="38"/>
       <c r="C42" s="9" t="s">
         <v>176</v>
       </c>
@@ -3979,10 +3979,10 @@
         <v>175</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="9" t="s">
@@ -3999,7 +3999,7 @@
         <v>10</v>
       </c>
       <c r="N42" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O42" s="11">
         <v>0.28860000000000002</v>
@@ -4022,7 +4022,7 @@
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="36" t="s">
         <v>227</v>
       </c>
       <c r="C43" s="9" t="s">
@@ -4041,7 +4041,7 @@
         <v>233</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="9" t="s">
@@ -4058,7 +4058,7 @@
         <v>5</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O43" s="11">
         <v>0.18729999999999999</v>
@@ -4080,7 +4080,7 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="B44" s="34"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="9" t="s">
         <v>183</v>
       </c>
@@ -4094,10 +4094,10 @@
         <v>182</v>
       </c>
       <c r="G44" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>313</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>314</v>
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="9" t="s">
@@ -4114,7 +4114,7 @@
         <v>5</v>
       </c>
       <c r="N44" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O44" s="11">
         <v>0.3478</v>
@@ -4137,7 +4137,7 @@
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="B45" s="34"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="9" t="s">
         <v>187</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>233</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="9" t="s">
@@ -4171,7 +4171,7 @@
         <v>5</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O45" s="11">
         <v>1.5923</v>
@@ -4194,7 +4194,7 @@
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="B46" s="34"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="9" t="s">
         <v>191</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>190</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -4226,7 +4226,7 @@
         <v>5</v>
       </c>
       <c r="N46" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O46" s="11">
         <v>0.34639999999999999</v>
@@ -4249,7 +4249,7 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="B47" s="34"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="9" t="s">
         <v>195</v>
       </c>
@@ -4263,10 +4263,10 @@
         <v>194</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="9" t="s">
@@ -4283,7 +4283,7 @@
         <v>5</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O47" s="11">
         <v>0.30620000000000003</v>
@@ -4306,7 +4306,7 @@
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="B48" s="34"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="9" t="s">
         <v>199</v>
       </c>
@@ -4361,7 +4361,7 @@
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="B49" s="35"/>
+      <c r="B49" s="38"/>
       <c r="C49" s="9" t="s">
         <v>203</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>202</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -4393,7 +4393,7 @@
         <v>5</v>
       </c>
       <c r="N49" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O49" s="11">
         <v>1.92</v>
@@ -4416,7 +4416,7 @@
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="B50" s="32" t="s">
+      <c r="B50" s="28" t="s">
         <v>228</v>
       </c>
       <c r="C50" s="9" t="s">
@@ -4432,10 +4432,10 @@
         <v>74</v>
       </c>
       <c r="G50" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="H50" s="5" t="s">
         <v>317</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>318</v>
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="9" t="s">
@@ -4452,7 +4452,7 @@
         <v>5</v>
       </c>
       <c r="N50" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O50" s="11">
         <v>1.8448</v>
@@ -4475,7 +4475,7 @@
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B51" s="32"/>
+      <c r="B51" s="28"/>
       <c r="C51" s="9" t="s">
         <v>78</v>
       </c>
@@ -4489,10 +4489,10 @@
         <v>77</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="9" t="s">
@@ -4509,7 +4509,7 @@
         <v>10</v>
       </c>
       <c r="N51" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O51" s="11">
         <v>0.72860000000000003</v>
@@ -4532,7 +4532,7 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B52" s="32"/>
+      <c r="B52" s="28"/>
       <c r="C52" s="9" t="s">
         <v>81</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>80</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -4564,24 +4564,24 @@
         <v>5</v>
       </c>
       <c r="N52" s="15" t="s">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="O52" s="11">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="P52" s="12">
         <f t="shared" si="3"/>
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="Q52" s="11">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="R52" s="12">
         <f t="shared" si="2"/>
-        <v>6.35</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="S52" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
@@ -4589,7 +4589,7 @@
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="B53" s="32"/>
+      <c r="B53" s="28"/>
       <c r="C53" s="9" t="s">
         <v>84</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>83</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -4643,7 +4643,7 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="B54" s="32"/>
+      <c r="B54" s="28"/>
       <c r="C54" s="9" t="s">
         <v>97</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>96</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -4675,7 +4675,7 @@
         <v>10</v>
       </c>
       <c r="N54" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O54" s="11">
         <v>1.61</v>
@@ -4698,7 +4698,7 @@
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B55" s="32"/>
+      <c r="B55" s="28"/>
       <c r="C55" s="9" t="s">
         <v>104</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>107</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -4730,7 +4730,7 @@
         <v>10</v>
       </c>
       <c r="N55" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O55" s="11">
         <v>0.19</v>
@@ -4750,7 +4750,7 @@
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="B56" s="32"/>
+      <c r="B56" s="28"/>
       <c r="C56" s="16" t="s">
         <v>100</v>
       </c>
@@ -4780,7 +4780,7 @@
       <c r="N56" s="17"/>
       <c r="O56" s="17"/>
       <c r="P56" s="18">
-        <f t="shared" ref="P56:P57" si="6">O56*L56</f>
+        <f t="shared" ref="P56:P57" si="9">O56*L56</f>
         <v>0</v>
       </c>
       <c r="Q56" s="19"/>
@@ -4822,7 +4822,7 @@
       <c r="N57" s="17"/>
       <c r="O57" s="17"/>
       <c r="P57" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q57" s="19"/>
@@ -4844,18 +4844,18 @@
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
       <c r="M58" s="24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N58" s="24"/>
       <c r="O58" s="25"/>
       <c r="P58" s="26">
         <f>SUM(P3:P55)</f>
-        <v>73.207199999999986</v>
+        <v>73.677199999999985</v>
       </c>
       <c r="Q58" s="24"/>
       <c r="R58" s="27">
         <f>SUM(R3:R55)</f>
-        <v>245.90749999999994</v>
+        <v>248.25749999999994</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -4961,11 +4961,10 @@
     <hyperlink ref="N55" r:id="rId49" xr:uid="{AABF823B-413E-4EC2-B954-DF074731CAA7}"/>
     <hyperlink ref="N48" r:id="rId50" xr:uid="{1114458F-A78D-4A76-B1CF-305337F52263}"/>
     <hyperlink ref="N53" r:id="rId51" xr:uid="{1E96E8EA-3806-41F4-BDB9-DF5C3FCF6928}"/>
-    <hyperlink ref="N52" r:id="rId52" xr:uid="{9B362694-4504-4DC6-95D1-20D4F3BD5DDD}"/>
-    <hyperlink ref="N41" r:id="rId53" xr:uid="{2F6C76CB-7AFF-4E6D-9732-3183EF2507E8}"/>
+    <hyperlink ref="N41" r:id="rId52" xr:uid="{2F6C76CB-7AFF-4E6D-9732-3183EF2507E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId54"/>
+  <pageSetup orientation="portrait" r:id="rId53"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Deliverables/SM_Top Board/_BOM/SM_Top_PCB_LCSC.xlsx
+++ b/Deliverables/SM_Top Board/_BOM/SM_Top_PCB_LCSC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20376"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Github\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4060B9E-6605-424E-A422-D3FAD764FA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08183F3-093D-4EEB-971F-D4617E5FCF17}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="332">
   <si>
     <t>Description</t>
   </si>
@@ -39,9 +39,6 @@
     <t>220uF</t>
   </si>
   <si>
-    <t>220uF ±20% 63V 10mm 14.5mm 1.2A 100kHz 10000hrs 105? -55?~+105? SMD,10x14.5mm Aluminum Electrolytic Capacitors - SMD RoHS</t>
-  </si>
-  <si>
     <t>C1, C22</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>470uF</t>
   </si>
   <si>
-    <t>470uF ±20% 50V 12.5mm 13.5mm 1000hrs 105? -40?~+105? SMD,12.5x13.5mm Aluminum Electrolytic Capacitors - SMD RoHS</t>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
@@ -93,9 +87,6 @@
     <t>68uF</t>
   </si>
   <si>
-    <t>68uF ±20% 50V 6.3mm 10mm 390mA 6.3x10mm Aluminum Electrolytic Capacitors - SMD RoHS</t>
-  </si>
-  <si>
     <t>C5</t>
   </si>
   <si>
@@ -132,9 +123,6 @@
     <t>22uF</t>
   </si>
   <si>
-    <t>22uF ±20% 35V X5R 0805 Multilayer Ceramic Capacitors MLCC - SMD/SMT RoHS</t>
-  </si>
-  <si>
     <t>C8</t>
   </si>
   <si>
@@ -324,9 +312,6 @@
     <t>P1, P2</t>
   </si>
   <si>
-    <t>Test Point</t>
-  </si>
-  <si>
     <t>Test Point ON</t>
   </si>
   <si>
@@ -336,9 +321,6 @@
     <t>TEST POINT</t>
   </si>
   <si>
-    <t>61300211121</t>
-  </si>
-  <si>
     <t>CONN HEADER VERT 2POS 2.54MM</t>
   </si>
   <si>
@@ -672,9 +654,6 @@
     <t>Quantity 5</t>
   </si>
   <si>
-    <t>DigiKey Link</t>
-  </si>
-  <si>
     <t>Unit Cost(1)</t>
   </si>
   <si>
@@ -762,27 +741,12 @@
     <t>Kyocera AVX</t>
   </si>
   <si>
-    <t>Vishay Semiconductors</t>
-  </si>
-  <si>
-    <t>Nexperia</t>
-  </si>
-  <si>
     <t>Worldsemi</t>
   </si>
   <si>
-    <t>SunLED</t>
-  </si>
-  <si>
     <t>Bel</t>
   </si>
   <si>
-    <t>Infineon</t>
-  </si>
-  <si>
-    <t>Remarks for senior reviewer</t>
-  </si>
-  <si>
     <t>Harwin Inc.</t>
   </si>
   <si>
@@ -882,9 +846,6 @@
     <t>Heisener</t>
   </si>
   <si>
-    <t>---------------</t>
-  </si>
-  <si>
     <t>C153291</t>
   </si>
   <si>
@@ -994,6 +955,72 @@
   </si>
   <si>
     <t>Local Supplier</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>220uF ±20% 63V 10mm 14.5mm 1.2A SMD RoHS</t>
+  </si>
+  <si>
+    <t>470uF ±20% 50V 12.5mm 13.5mm SMD RoHS</t>
+  </si>
+  <si>
+    <t>68uF ±20% 50V 6.3mm 10mm 390mA SMD RoHS</t>
+  </si>
+  <si>
+    <t>22uF ±20% 35V X5R 0805- SMD/SMT RoHS</t>
+  </si>
+  <si>
+    <t>Quantity 25</t>
+  </si>
+  <si>
+    <t>Quantity 100</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Unit Cost (25 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (25)</t>
+  </si>
+  <si>
+    <t>Unit Cost (100 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (100)</t>
+  </si>
+  <si>
+    <t>-------</t>
+  </si>
+  <si>
+    <t>0.01uF</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>C376821</t>
+  </si>
+  <si>
+    <t>TCC0603X7R223K101CT</t>
+  </si>
+  <si>
+    <t>---------</t>
+  </si>
+  <si>
+    <t>-----</t>
+  </si>
+  <si>
+    <t>Everlight Elec</t>
+  </si>
+  <si>
+    <t>--------</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +1031,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1086,8 +1113,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1112,8 +1154,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1215,13 +1263,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1239,9 +1378,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1302,9 +1438,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="5" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1333,6 +1466,81 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1617,885 +1825,1208 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:Y59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" customWidth="1"/>
-    <col min="10" max="11" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="19.5703125" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" customWidth="1"/>
-    <col min="19" max="19" width="30.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="12.5703125" customWidth="1"/>
+    <col min="25" max="25" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+    </row>
+    <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="J2" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="34"/>
+      <c r="K2" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="M2" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="N2" s="47" t="s">
+        <v>315</v>
+      </c>
+      <c r="O2" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q2" s="47" t="s">
+        <v>209</v>
+      </c>
+      <c r="R2" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="S2" s="48" t="s">
+        <v>211</v>
+      </c>
+      <c r="T2" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="U2" s="48" t="s">
+        <v>319</v>
+      </c>
+      <c r="V2" s="47" t="s">
+        <v>320</v>
+      </c>
+      <c r="W2" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="X2" s="47" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y2" s="49" t="s">
+        <v>318</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6" t="s">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="B3" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="40">
+        <v>1</v>
+      </c>
+      <c r="L3" s="42">
         <v>2</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>1</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="9">
-        <v>1</v>
-      </c>
-      <c r="L3" s="10">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
+      <c r="M3" s="43">
         <f>L3*5</f>
         <v>10</v>
       </c>
-      <c r="N3" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O3" s="11">
-        <v>0.24909999999999999</v>
-      </c>
-      <c r="P3" s="12">
-        <f>O3*L3</f>
-        <v>0.49819999999999998</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>0.19189999999999999</v>
-      </c>
-      <c r="R3" s="12">
-        <f>Q3*M3</f>
-        <v>1.9189999999999998</v>
-      </c>
-      <c r="S3" s="5"/>
+      <c r="N3" s="43">
+        <f>L3*25</f>
+        <v>50</v>
+      </c>
+      <c r="O3" s="43">
+        <f>L3*100</f>
+        <v>200</v>
+      </c>
+      <c r="P3" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q3" s="45">
+        <v>0.25669999999999998</v>
+      </c>
+      <c r="R3" s="46">
+        <f>Q3*L3</f>
+        <v>0.51339999999999997</v>
+      </c>
+      <c r="S3" s="45">
+        <v>0.19850000000000001</v>
+      </c>
+      <c r="T3" s="46">
+        <f>S3*M3</f>
+        <v>1.9850000000000001</v>
+      </c>
+      <c r="U3" s="46">
+        <v>0.18790000000000001</v>
+      </c>
+      <c r="V3" s="46">
+        <f>U3*N3</f>
+        <v>9.3950000000000014</v>
+      </c>
+      <c r="W3" s="46">
+        <v>0.1772</v>
+      </c>
+      <c r="X3" s="46">
+        <f>W3*O3</f>
+        <v>35.44</v>
+      </c>
+      <c r="Y3" s="43"/>
     </row>
-    <row r="4" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="9">
+      <c r="G4" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="8">
         <v>50</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>8</v>
       </c>
       <c r="M4" s="5">
         <f t="shared" ref="M4:M57" si="0">L4*5</f>
         <v>40</v>
       </c>
-      <c r="N4" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O4" s="11">
+      <c r="N4" s="43">
+        <f t="shared" ref="N4:N57" si="1">L4*25</f>
+        <v>200</v>
+      </c>
+      <c r="O4" s="43">
+        <f t="shared" ref="O4:O57" si="2">L4*100</f>
+        <v>800</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q4" s="10">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="P4" s="12">
-        <f>O4*K4</f>
-        <v>0.2</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="R4" s="12">
+      <c r="R4" s="11">
         <f>Q4*K4</f>
         <v>0.2</v>
       </c>
-      <c r="S4" s="5"/>
+      <c r="S4" s="10">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T4" s="11">
+        <f>S4*K4</f>
+        <v>0.2</v>
+      </c>
+      <c r="U4" s="11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="V4" s="46">
+        <f t="shared" ref="V4:V57" si="3">U4*N4</f>
+        <v>0.8</v>
+      </c>
+      <c r="W4" s="11">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="X4" s="46">
+        <f t="shared" ref="X4:X57" si="4">W4*O4</f>
+        <v>2.48</v>
+      </c>
+      <c r="Y4" s="5"/>
     </row>
-    <row r="5" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <f t="shared" ref="A5:A56" si="1">A4+1</f>
+    <row r="5" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <f t="shared" ref="A5:A57" si="5">A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="9">
+      <c r="G5" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="8">
         <v>5</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="9">
         <v>1</v>
       </c>
       <c r="M5" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O5" s="11">
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="P5" s="12">
-        <f>O5*K5</f>
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="R5" s="12">
-        <f>Q5*M5</f>
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>267</v>
+      <c r="N5" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O5" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>0.1045</v>
+      </c>
+      <c r="R5" s="11">
+        <f>Q5*K5</f>
+        <v>0.52249999999999996</v>
+      </c>
+      <c r="S5" s="10">
+        <v>0.1045</v>
+      </c>
+      <c r="T5" s="11">
+        <f>S5*M5</f>
+        <v>0.52249999999999996</v>
+      </c>
+      <c r="U5" s="11">
+        <v>0.1045</v>
+      </c>
+      <c r="V5" s="46">
+        <f t="shared" si="3"/>
+        <v>2.6124999999999998</v>
+      </c>
+      <c r="W5" s="11">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="X5" s="46">
+        <f t="shared" si="4"/>
+        <v>8.33</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>255</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <f t="shared" si="1"/>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="9">
+      <c r="G6" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="8">
         <v>1</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>1</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O6" s="11">
+      <c r="N6" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O6" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q6" s="10">
         <v>0.4869</v>
       </c>
-      <c r="P6" s="12">
-        <f>O6*L6</f>
+      <c r="R6" s="11">
+        <f>Q6*L6</f>
         <v>0.4869</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="S6" s="10">
         <v>0.4869</v>
       </c>
-      <c r="R6" s="12">
-        <f t="shared" ref="R6:R54" si="2">Q6*M6</f>
+      <c r="T6" s="11">
+        <f t="shared" ref="T6:T54" si="6">S6*M6</f>
         <v>2.4344999999999999</v>
       </c>
-      <c r="S6" s="5"/>
+      <c r="U6" s="11">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="V6" s="46">
+        <f t="shared" si="3"/>
+        <v>9.7850000000000001</v>
+      </c>
+      <c r="W6" s="11">
+        <v>0.3553</v>
+      </c>
+      <c r="X6" s="46">
+        <f t="shared" si="4"/>
+        <v>35.53</v>
+      </c>
+      <c r="Y6" s="5"/>
     </row>
-    <row r="7" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <f t="shared" si="1"/>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="9" t="s">
+      <c r="B7" s="33"/>
+      <c r="C7" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="9">
+      <c r="G7" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="8">
         <v>10</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>1</v>
       </c>
       <c r="M7" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N7" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O7" s="11">
+      <c r="N7" s="43">
+        <v>30</v>
+      </c>
+      <c r="O7" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q7" s="10">
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="P7" s="12">
-        <f>O7*K7</f>
-        <v>0.71099999999999997</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>7.1099999999999997E-2</v>
-      </c>
-      <c r="R7" s="12">
+      <c r="R7" s="11">
         <f>Q7*K7</f>
         <v>0.71099999999999997</v>
       </c>
-      <c r="S7" s="5"/>
+      <c r="S7" s="10">
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="T7" s="11">
+        <f>S7*K7</f>
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="U7" s="11">
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="V7" s="46">
+        <f t="shared" si="3"/>
+        <v>2.133</v>
+      </c>
+      <c r="W7" s="11">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="X7" s="46">
+        <f t="shared" si="4"/>
+        <v>5.4</v>
+      </c>
+      <c r="Y7" s="5"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <f t="shared" si="1"/>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="9" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="9">
+      <c r="G8" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="8">
         <v>50</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <v>1</v>
       </c>
       <c r="M8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N8" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O8" s="11">
-        <v>5.3E-3</v>
-      </c>
-      <c r="P8" s="12">
-        <f>O8*K8</f>
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>5.3E-3</v>
-      </c>
-      <c r="R8" s="12">
+      <c r="N8" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O8" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R8" s="11">
         <f>Q8*K8</f>
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="S8" s="5"/>
+        <v>0.2</v>
+      </c>
+      <c r="S8" s="10">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T8" s="11">
+        <f>S8*K8</f>
+        <v>0.2</v>
+      </c>
+      <c r="U8" s="11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="V8" s="46">
+        <f>U8*K8</f>
+        <v>0.2</v>
+      </c>
+      <c r="W8" s="11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="X8" s="46">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="Y8" s="5"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <f t="shared" si="1"/>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="33"/>
+      <c r="C9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="9">
+      <c r="G9" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="8">
         <v>20</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <v>1</v>
       </c>
       <c r="M9" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="N9" s="43">
+        <v>40</v>
+      </c>
+      <c r="O9" s="43">
+        <v>120</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="R9" s="11">
+        <f>Q9*K9</f>
+        <v>0.624</v>
+      </c>
+      <c r="S9" s="10">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="T9" s="11">
+        <f>S9*K9</f>
+        <v>0.624</v>
+      </c>
+      <c r="U9" s="11">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="V9" s="46">
+        <f t="shared" si="3"/>
+        <v>1.248</v>
+      </c>
+      <c r="W9" s="11">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="X9" s="46">
+        <f t="shared" si="4"/>
+        <v>3.7439999999999998</v>
+      </c>
+      <c r="Y9" s="5"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="O9" s="11">
-        <v>3.27E-2</v>
-      </c>
-      <c r="P9" s="12">
-        <f>O9*K9</f>
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>3.27E-2</v>
-      </c>
-      <c r="R9" s="12">
-        <f>Q9*K9</f>
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="S9" s="5"/>
+      <c r="I10" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1</v>
+      </c>
+      <c r="L10" s="9">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>7</v>
+      </c>
+      <c r="N10" s="43">
+        <v>27</v>
+      </c>
+      <c r="O10" s="43">
+        <v>105</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0.25950000000000001</v>
+      </c>
+      <c r="R10" s="11">
+        <f t="shared" ref="R10:R54" si="7">Q10*L10</f>
+        <v>0.25950000000000001</v>
+      </c>
+      <c r="S10" s="10">
+        <v>0.25950000000000001</v>
+      </c>
+      <c r="T10" s="11">
+        <f t="shared" si="6"/>
+        <v>1.8165</v>
+      </c>
+      <c r="U10" s="11">
+        <v>0.18920000000000001</v>
+      </c>
+      <c r="V10" s="46">
+        <f t="shared" si="3"/>
+        <v>5.1084000000000005</v>
+      </c>
+      <c r="W10" s="11">
+        <v>0.1633</v>
+      </c>
+      <c r="X10" s="46">
+        <f t="shared" si="4"/>
+        <v>17.1465</v>
+      </c>
+      <c r="Y10" s="5"/>
     </row>
-    <row r="10" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="9" t="s">
+    <row r="11" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="33"/>
+      <c r="C11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="9">
-        <v>1</v>
-      </c>
-      <c r="L10" s="10">
-        <v>1</v>
-      </c>
-      <c r="M10" s="5">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N10" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O10" s="11">
-        <v>0.30170000000000002</v>
-      </c>
-      <c r="P10" s="12">
-        <f t="shared" ref="P10:P54" si="3">O10*L10</f>
-        <v>0.30170000000000002</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0.30170000000000002</v>
-      </c>
-      <c r="R10" s="12">
-        <f t="shared" si="2"/>
-        <v>1.5085000000000002</v>
-      </c>
-      <c r="S10" s="5"/>
-    </row>
-    <row r="11" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="9">
+      <c r="G11" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="8">
         <v>50</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="9">
         <v>1</v>
       </c>
       <c r="M11" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N11" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O11" s="11">
+      <c r="N11" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O11" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q11" s="10">
         <v>1.2200000000000001E-2</v>
       </c>
-      <c r="P11" s="12">
-        <f t="shared" ref="P11:P16" si="4">O11*K11</f>
+      <c r="R11" s="11">
+        <f t="shared" ref="R11:R16" si="8">Q11*K11</f>
         <v>0.61</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="S11" s="10">
         <v>1.2200000000000001E-2</v>
       </c>
-      <c r="R11" s="12">
-        <f>Q11*K11</f>
+      <c r="T11" s="11">
+        <f>S11*K11</f>
         <v>0.61</v>
       </c>
-      <c r="S11" s="5"/>
+      <c r="U11" s="11">
+        <v>0.1633</v>
+      </c>
+      <c r="V11" s="11">
+        <v>0.61</v>
+      </c>
+      <c r="W11" s="11">
+        <v>1.21E-2</v>
+      </c>
+      <c r="X11" s="46">
+        <f t="shared" si="4"/>
+        <v>1.21</v>
+      </c>
+      <c r="Y11" s="5"/>
     </row>
-    <row r="12" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
-        <f t="shared" si="1"/>
+    <row r="12" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="8">
+        <v>10</v>
+      </c>
+      <c r="L12" s="9">
+        <v>5</v>
+      </c>
+      <c r="M12" s="5">
+        <v>30</v>
+      </c>
+      <c r="N12" s="43">
+        <v>130</v>
+      </c>
+      <c r="O12" s="43">
+        <v>520</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="R12" s="11">
+        <f t="shared" si="8"/>
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="S12" s="10">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="T12" s="11">
+        <f>S12*30</f>
+        <v>1.179</v>
+      </c>
+      <c r="U12" s="11">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="V12" s="46">
+        <f t="shared" si="3"/>
+        <v>3.835</v>
+      </c>
+      <c r="W12" s="11">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="X12" s="46">
+        <f t="shared" si="4"/>
+        <v>14.404</v>
+      </c>
+      <c r="Y12" s="5"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="E13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="I12" s="21"/>
-      <c r="J12" s="9" t="s">
+      <c r="G13" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="9">
-        <v>10</v>
-      </c>
-      <c r="L12" s="10">
-        <v>5</v>
-      </c>
-      <c r="M12" s="5">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="N12" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O12" s="11">
-        <v>3.9300000000000002E-2</v>
-      </c>
-      <c r="P12" s="12">
-        <f t="shared" si="4"/>
-        <v>0.39300000000000002</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>3.9300000000000002E-2</v>
-      </c>
-      <c r="R12" s="12">
-        <f>Q12*30</f>
-        <v>1.179</v>
-      </c>
-      <c r="S12" s="5"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" s="9">
+      <c r="K13" s="8">
         <v>20</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="9">
         <v>2</v>
       </c>
       <c r="M13" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N13" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O13" s="11">
+      <c r="N13" s="43">
+        <v>60</v>
+      </c>
+      <c r="O13" s="43">
+        <v>220</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q13" s="10">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="P13" s="12">
+      <c r="R13" s="11">
+        <f t="shared" si="8"/>
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="S13" s="10">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="T13" s="11">
+        <f>S13*K13</f>
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="U13" s="11">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="V13" s="46">
+        <f t="shared" si="3"/>
+        <v>1.554</v>
+      </c>
+      <c r="W13" s="11">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="X13" s="46">
         <f t="shared" si="4"/>
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>2.5899999999999999E-2</v>
-      </c>
-      <c r="R13" s="12">
-        <f>Q13*K13</f>
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="S13" s="5"/>
+        <v>4.0919999999999996</v>
+      </c>
+      <c r="Y13" s="5"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <f t="shared" si="1"/>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="B14" s="33"/>
+      <c r="C14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="K14" s="8">
         <v>50</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="I14" s="22"/>
-      <c r="J14" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="K14" s="9">
-        <v>50</v>
-      </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <v>2</v>
       </c>
       <c r="M14" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N14" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O14" s="11">
+      <c r="N14" s="43">
+        <v>100</v>
+      </c>
+      <c r="O14" s="43">
+        <v>250</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q14" s="10">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="P14" s="12">
+      <c r="R14" s="11">
+        <f t="shared" si="8"/>
+        <v>0.375</v>
+      </c>
+      <c r="S14" s="10">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="T14" s="11">
+        <f>S14*K14</f>
+        <v>0.375</v>
+      </c>
+      <c r="U14" s="11">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="V14" s="46">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="W14" s="11">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="X14" s="46">
         <f t="shared" si="4"/>
-        <v>0.375</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="R14" s="12">
-        <f>Q14*K14</f>
-        <v>0.375</v>
-      </c>
-      <c r="S14" s="5"/>
+        <v>1.875</v>
+      </c>
+      <c r="Y14" s="5"/>
     </row>
-    <row r="15" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <f t="shared" si="1"/>
+    <row r="15" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>282</v>
+      <c r="B15" s="33"/>
+      <c r="C15" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>248</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="K15" s="9">
+        <v>271</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="8">
         <v>20</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="9">
         <v>4</v>
       </c>
       <c r="M15" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N15" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O15" s="11">
+      <c r="N15" s="43">
+        <v>120</v>
+      </c>
+      <c r="O15" s="43">
+        <v>420</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q15" s="10">
         <v>1.9300000000000001E-2</v>
       </c>
-      <c r="P15" s="12">
+      <c r="R15" s="11">
+        <f t="shared" si="8"/>
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="S15" s="10">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="T15" s="11">
+        <f t="shared" si="6"/>
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="U15" s="11">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="V15" s="46">
+        <f t="shared" si="3"/>
+        <v>2.3160000000000003</v>
+      </c>
+      <c r="W15" s="11">
+        <v>1.44E-2</v>
+      </c>
+      <c r="X15" s="46">
         <f t="shared" si="4"/>
-        <v>0.38600000000000001</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>1.9300000000000001E-2</v>
-      </c>
-      <c r="R15" s="12">
-        <f t="shared" si="2"/>
-        <v>0.38600000000000001</v>
-      </c>
-      <c r="S15" s="13"/>
+        <v>6.048</v>
+      </c>
+      <c r="Y15" s="12"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <f>A15+1</f>
         <v>14</v>
       </c>
-      <c r="B16" s="35"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I16" s="23"/>
+        <v>269</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>325</v>
+      </c>
       <c r="J16" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K16" s="2">
         <v>10</v>
@@ -2507,2361 +3038,3102 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N16" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O16" s="4">
-        <v>4.9399999999999999E-2</v>
-      </c>
-      <c r="P16" s="12">
-        <f t="shared" si="4"/>
-        <v>0.49399999999999999</v>
+      <c r="N16" s="43">
+        <v>110</v>
+      </c>
+      <c r="O16" s="43">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="Q16" s="4">
         <v>4.9399999999999999E-2</v>
       </c>
-      <c r="R16" s="12">
-        <f t="shared" si="2"/>
+      <c r="R16" s="11">
+        <f t="shared" si="8"/>
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="S16" s="4">
+        <v>4.9399999999999999E-2</v>
+      </c>
+      <c r="T16" s="11">
+        <f t="shared" si="6"/>
         <v>0.98799999999999999</v>
       </c>
-      <c r="S16" s="5"/>
+      <c r="U16" s="11">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="V16" s="46">
+        <f t="shared" si="3"/>
+        <v>3.8940000000000001</v>
+      </c>
+      <c r="W16" s="11">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="X16" s="46">
+        <f t="shared" si="4"/>
+        <v>13.16</v>
+      </c>
+      <c r="Y16" s="5"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
-        <f t="shared" si="1"/>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" s="9">
-        <v>1</v>
-      </c>
-      <c r="L17" s="10">
+      <c r="B17" s="33"/>
+      <c r="C17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="8">
+        <v>50</v>
+      </c>
+      <c r="L17" s="9">
         <v>1</v>
       </c>
       <c r="M17" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N17" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="O17" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="P17" s="12">
-        <f t="shared" si="3"/>
-        <v>0.1</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="R17" s="12">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="S17" s="5"/>
+      <c r="N17" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O17" s="43">
+        <v>150</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="R17" s="11">
+        <f>Q17*K17</f>
+        <v>0.25</v>
+      </c>
+      <c r="S17" s="10">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="T17" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="U17" s="11">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="V17" s="46">
+        <v>0.25</v>
+      </c>
+      <c r="W17" s="11">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X17" s="46">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
+      </c>
+      <c r="Y17" s="5"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
-        <f t="shared" si="1"/>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="33"/>
+      <c r="C18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="I18" s="20"/>
-      <c r="J18" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="K18" s="9">
+      <c r="G18" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="8">
         <v>20</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>1</v>
       </c>
       <c r="M18" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N18" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O18" s="11">
-        <v>3.27E-2</v>
-      </c>
-      <c r="P18" s="12">
-        <f>O18*K18</f>
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="Q18" s="31">
-        <v>3.27E-2</v>
-      </c>
-      <c r="R18" s="12">
+      <c r="N18" s="43">
+        <v>40</v>
+      </c>
+      <c r="O18" s="43">
+        <v>120</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="R18" s="11">
         <f>Q18*K18</f>
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="S18" s="13"/>
+        <v>0.624</v>
+      </c>
+      <c r="S18" s="29">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="T18" s="11">
+        <f>S18*K18</f>
+        <v>0.624</v>
+      </c>
+      <c r="U18" s="11">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="V18" s="46">
+        <f t="shared" si="3"/>
+        <v>1.248</v>
+      </c>
+      <c r="W18" s="11">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="X18" s="46">
+        <f t="shared" si="4"/>
+        <v>3.7439999999999998</v>
+      </c>
+      <c r="Y18" s="12"/>
     </row>
-    <row r="19" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
-        <f t="shared" si="1"/>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="B19" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="I19" s="22"/>
-      <c r="J19" s="9" t="s">
+      <c r="B19" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="K19" s="9">
+      <c r="G19" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="I19" s="60" t="s">
+        <v>323</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="8">
         <v>50</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>4</v>
       </c>
       <c r="M19" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N19" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O19" s="11">
+      <c r="N19" s="43">
+        <v>150</v>
+      </c>
+      <c r="O19" s="43">
+        <v>450</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q19" s="10">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="P19" s="12">
-        <f>O19*K19</f>
-        <v>0.23500000000000001</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="R19" s="12">
+      <c r="R19" s="11">
         <f>Q19*K19</f>
         <v>0.23500000000000001</v>
       </c>
-      <c r="S19" s="5"/>
+      <c r="S19" s="10">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="T19" s="11">
+        <f>S19*K19</f>
+        <v>0.23500000000000001</v>
+      </c>
+      <c r="U19" s="11">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="V19" s="46">
+        <f t="shared" si="3"/>
+        <v>0.70500000000000007</v>
+      </c>
+      <c r="W19" s="11">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="X19" s="46">
+        <f t="shared" si="4"/>
+        <v>2.1150000000000002</v>
+      </c>
+      <c r="Y19" s="5"/>
     </row>
-    <row r="20" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
-        <f t="shared" si="1"/>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="I20" s="22"/>
-      <c r="J20" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="K20" s="9">
+      <c r="B20" s="35"/>
+      <c r="C20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="F20" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="I20" s="21"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8">
         <v>1</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>1</v>
       </c>
       <c r="M20" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N20" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="O20" s="4">
-        <v>0.66</v>
-      </c>
-      <c r="P20" s="12">
-        <f t="shared" si="3"/>
-        <v>0.66</v>
+      <c r="N20" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O20" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>272</v>
       </c>
       <c r="Q20" s="4">
         <v>0.66</v>
       </c>
-      <c r="R20" s="12">
-        <f t="shared" si="2"/>
+      <c r="R20" s="11">
+        <f t="shared" si="7"/>
+        <v>0.66</v>
+      </c>
+      <c r="S20" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="T20" s="11">
+        <f t="shared" si="6"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="S20" s="13"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="11"/>
+      <c r="X20" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="12"/>
     </row>
-    <row r="21" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
-        <f t="shared" si="1"/>
+    <row r="21" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="K21" s="9">
+      <c r="B21" s="35"/>
+      <c r="C21" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="58"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8">
         <v>5</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <v>8</v>
       </c>
       <c r="M21" s="5">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N21" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="O21" s="4">
+      <c r="N21" s="43">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="O21" s="43">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q21" s="4">
         <v>0.36</v>
       </c>
-      <c r="P21" s="12">
-        <f>O21*10</f>
+      <c r="R21" s="11">
+        <f>Q21*10</f>
         <v>3.5999999999999996</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="S21" s="4">
         <v>0.24099999999999999</v>
       </c>
-      <c r="R21" s="12">
-        <f>(Q21*25)+(0.284*10)+(0.36*5)</f>
+      <c r="T21" s="11">
+        <f>(S21*25)+(0.284*10)+(0.36*5)</f>
         <v>10.664999999999999</v>
       </c>
-      <c r="S21" s="13"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="11"/>
+      <c r="X21" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="12"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
-        <f t="shared" si="1"/>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="I22" s="22"/>
-      <c r="J22" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="K22" s="9">
+      <c r="B22" s="35"/>
+      <c r="C22" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22" s="60" t="s">
+        <v>328</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="K22" s="8">
         <v>5</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="9">
         <v>1</v>
       </c>
       <c r="M22" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N22" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O22" s="11">
+      <c r="N22" s="43">
+        <v>30</v>
+      </c>
+      <c r="O22" s="43">
+        <v>120</v>
+      </c>
+      <c r="P22" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q22" s="10">
         <v>0.14299999999999999</v>
       </c>
-      <c r="P22" s="12">
-        <f>O22*K22</f>
+      <c r="R22" s="11">
+        <f>Q22*K22</f>
         <v>0.71499999999999997</v>
       </c>
-      <c r="Q22" s="11">
+      <c r="S22" s="10">
         <v>0.14299999999999999</v>
       </c>
-      <c r="R22" s="12">
-        <f t="shared" si="2"/>
+      <c r="T22" s="11">
+        <f t="shared" si="6"/>
         <v>0.71499999999999997</v>
       </c>
-      <c r="S22" s="5"/>
+      <c r="U22" s="11">
+        <v>0.1326</v>
+      </c>
+      <c r="V22" s="46">
+        <f t="shared" si="3"/>
+        <v>3.9779999999999998</v>
+      </c>
+      <c r="W22" s="11">
+        <v>0.1011</v>
+      </c>
+      <c r="X22" s="46">
+        <f t="shared" si="4"/>
+        <v>12.132</v>
+      </c>
+      <c r="Y22" s="5"/>
     </row>
-    <row r="23" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
-        <f t="shared" si="1"/>
+    <row r="23" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="K23" s="9">
+      <c r="B23" s="36"/>
+      <c r="C23" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>330</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="K23" s="8">
         <v>10</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="9">
         <v>1</v>
       </c>
       <c r="M23" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N23" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O23" s="4">
-        <v>7.5800000000000006E-2</v>
-      </c>
-      <c r="P23" s="12">
-        <f>O23*K23</f>
-        <v>0.75800000000000001</v>
+      <c r="N23" s="43">
+        <v>30</v>
+      </c>
+      <c r="O23" s="43">
+        <v>120</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="Q23" s="4">
-        <v>7.5800000000000006E-2</v>
-      </c>
-      <c r="R23" s="12">
+        <v>7.3099999999999998E-2</v>
+      </c>
+      <c r="R23" s="11">
         <f>Q23*K23</f>
-        <v>0.75800000000000001</v>
-      </c>
-      <c r="S23" s="13" t="s">
-        <v>291</v>
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="S23" s="4">
+        <v>7.3099999999999998E-2</v>
+      </c>
+      <c r="T23" s="11">
+        <f>S23*K23</f>
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="U23" s="11">
+        <v>7.3099999999999998E-2</v>
+      </c>
+      <c r="V23" s="46">
+        <f t="shared" si="3"/>
+        <v>2.1930000000000001</v>
+      </c>
+      <c r="W23" s="11">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="X23" s="46">
+        <f t="shared" si="4"/>
+        <v>6.8160000000000007</v>
+      </c>
+      <c r="Y23" s="12" t="s">
+        <v>278</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
-        <f t="shared" si="1"/>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K24" s="9">
+      <c r="B24" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="K24" s="8">
         <v>1</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="9">
         <v>1</v>
       </c>
       <c r="M24" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N24" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="O24" s="4">
-        <v>0.14899999999999999</v>
-      </c>
-      <c r="P24" s="12">
-        <f t="shared" si="3"/>
-        <v>0.14899999999999999</v>
+      <c r="N24" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O24" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>272</v>
       </c>
       <c r="Q24" s="4">
         <v>0.14899999999999999</v>
       </c>
-      <c r="R24" s="12">
-        <f t="shared" si="2"/>
+      <c r="R24" s="11">
+        <f t="shared" si="7"/>
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="S24" s="4">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="T24" s="11">
+        <f t="shared" si="6"/>
         <v>0.745</v>
       </c>
-      <c r="S24" s="5"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="11"/>
+      <c r="X24" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="5"/>
     </row>
-    <row r="25" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
-        <f t="shared" si="1"/>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="K25" s="9">
+      <c r="B25" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="K25" s="8">
         <v>1</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="9">
         <v>1</v>
       </c>
       <c r="M25" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N25" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O25" s="4">
-        <v>0.79710000000000003</v>
-      </c>
-      <c r="P25" s="12">
-        <f t="shared" si="3"/>
-        <v>0.79710000000000003</v>
+      <c r="N25" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O25" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="Q25" s="4">
         <v>0.79710000000000003</v>
       </c>
-      <c r="R25" s="12">
-        <f t="shared" si="2"/>
+      <c r="R25" s="11">
+        <f t="shared" si="7"/>
+        <v>0.79710000000000003</v>
+      </c>
+      <c r="S25" s="4">
+        <v>0.79710000000000003</v>
+      </c>
+      <c r="T25" s="11">
+        <f t="shared" si="6"/>
         <v>3.9855</v>
       </c>
-      <c r="S25" s="5"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="11"/>
+      <c r="X25" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="5"/>
     </row>
-    <row r="26" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
-        <f t="shared" si="1"/>
+    <row r="26" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="K26" s="9">
+      <c r="B26" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="K26" s="8">
         <v>1</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="9">
         <v>8</v>
       </c>
       <c r="M26" s="5">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N26" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O26" s="4">
-        <v>2.4777</v>
-      </c>
-      <c r="P26" s="12">
-        <f t="shared" si="3"/>
-        <v>19.8216</v>
+      <c r="N26" s="43">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="O26" s="43">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+      <c r="P26" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="Q26" s="4">
         <v>2.4777</v>
       </c>
-      <c r="R26" s="12">
-        <f t="shared" si="2"/>
+      <c r="R26" s="11">
+        <f t="shared" si="7"/>
+        <v>19.8216</v>
+      </c>
+      <c r="S26" s="4">
+        <v>2.4777</v>
+      </c>
+      <c r="T26" s="11">
+        <f t="shared" si="6"/>
         <v>99.108000000000004</v>
       </c>
-      <c r="S26" s="5"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="11"/>
+      <c r="X26" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="5"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
-        <f t="shared" si="1"/>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="B27" s="36" t="s">
-        <v>225</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K27" s="9">
+      <c r="B27" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K27" s="8">
         <v>100</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="9">
         <v>2</v>
       </c>
       <c r="M27" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N27" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O27" s="4">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="P27" s="12">
-        <f>O27*K27</f>
-        <v>0.16999999999999998</v>
+      <c r="N27" s="43">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="O27" s="43">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="P27" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="Q27" s="4">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="R27" s="12">
+      <c r="R27" s="11">
         <f>Q27*K27</f>
         <v>0.16999999999999998</v>
       </c>
-      <c r="S27" s="5"/>
+      <c r="S27" s="4">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="T27" s="11">
+        <f>S27*K27</f>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="U27" s="11"/>
+      <c r="V27" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="11"/>
+      <c r="X27" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="5"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
-        <f t="shared" si="1"/>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="K28" s="9">
+      <c r="B28" s="35"/>
+      <c r="C28" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28" s="8">
         <v>100</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="9">
         <v>2</v>
       </c>
       <c r="M28" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N28" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O28" s="4">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="P28" s="12">
-        <f>O28*K28</f>
-        <v>0.16999999999999998</v>
+      <c r="N28" s="43">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="O28" s="43">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="P28" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="Q28" s="4">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="R28" s="12">
+      <c r="R28" s="11">
         <f>Q28*K28</f>
         <v>0.16999999999999998</v>
       </c>
-      <c r="S28" s="5"/>
+      <c r="S28" s="4">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="T28" s="11">
+        <f>S28*K28</f>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="U28" s="11"/>
+      <c r="V28" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="11"/>
+      <c r="X28" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="5"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
-        <f t="shared" si="1"/>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="K29" s="9">
+      <c r="B29" s="35"/>
+      <c r="C29" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K29" s="8">
         <v>100</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="9">
         <v>1</v>
       </c>
       <c r="M29" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N29" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O29" s="4">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="P29" s="12">
-        <f>O29*K29</f>
-        <v>0.21</v>
+      <c r="N29" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O29" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P29" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="Q29" s="4">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="R29" s="12">
+      <c r="R29" s="11">
         <f>Q29*K29</f>
         <v>0.21</v>
       </c>
-      <c r="S29" s="5"/>
+      <c r="S29" s="4">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="T29" s="11">
+        <f>S29*K29</f>
+        <v>0.21</v>
+      </c>
+      <c r="U29" s="11"/>
+      <c r="V29" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="11"/>
+      <c r="X29" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="5"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
-        <f t="shared" si="1"/>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="K30" s="9">
+      <c r="B30" s="35"/>
+      <c r="C30" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="K30" s="8">
         <v>100</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="9">
         <v>1</v>
       </c>
       <c r="M30" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N30" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O30" s="11">
+      <c r="N30" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O30" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P30" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q30" s="10">
         <v>1.4E-3</v>
       </c>
-      <c r="P30" s="12">
-        <f t="shared" ref="P30:P31" si="5">O30*K30</f>
+      <c r="R30" s="11">
+        <f t="shared" ref="R30:R31" si="9">Q30*K30</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="Q30" s="11">
+      <c r="S30" s="10">
         <v>1.4E-3</v>
       </c>
-      <c r="R30" s="12">
-        <f t="shared" ref="R30:R31" si="6">Q30*K30</f>
+      <c r="T30" s="11">
+        <f t="shared" ref="T30:T31" si="10">S30*K30</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S30" s="5"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="11"/>
+      <c r="X30" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="5"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
-        <f t="shared" si="1"/>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>230</v>
+      <c r="B31" s="35"/>
+      <c r="C31" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="I31" s="5"/>
-      <c r="J31" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="K31" s="9">
+      <c r="J31" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K31" s="8">
         <v>100</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="9">
         <v>4</v>
       </c>
       <c r="M31" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N31" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O31" s="11">
+      <c r="N31" s="43">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="O31" s="43">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="P31" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q31" s="10">
         <v>2.3E-3</v>
       </c>
-      <c r="P31" s="12">
+      <c r="R31" s="11">
+        <f t="shared" si="9"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="S31" s="10">
+        <v>2.3E-3</v>
+      </c>
+      <c r="T31" s="11">
+        <f t="shared" si="10"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="U31" s="11"/>
+      <c r="V31" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="11"/>
+      <c r="X31" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="5"/>
+    </row>
+    <row r="32" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
         <f t="shared" si="5"/>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="Q31" s="11">
-        <v>2.3E-3</v>
-      </c>
-      <c r="R31" s="12">
-        <f t="shared" si="6"/>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="S31" s="5"/>
-    </row>
-    <row r="32" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
-        <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>136</v>
+      <c r="B32" s="35"/>
+      <c r="C32" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>300</v>
+        <v>222</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>287</v>
       </c>
       <c r="I32" s="5"/>
-      <c r="J32" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="K32" s="9">
+      <c r="J32" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="K32" s="8">
         <v>5</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="9">
         <v>4</v>
       </c>
       <c r="M32" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N32" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="O32" s="11">
+      <c r="N32" s="43">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="O32" s="43">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="P32" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q32" s="10">
         <v>8.5699999999999998E-2</v>
       </c>
-      <c r="P32" s="12">
-        <f t="shared" ref="P32:P40" si="7">O32*K32</f>
+      <c r="R32" s="11">
+        <f t="shared" ref="R32:R40" si="11">Q32*K32</f>
         <v>0.42849999999999999</v>
       </c>
-      <c r="Q32" s="11">
+      <c r="S32" s="10">
         <v>8.5699999999999998E-2</v>
       </c>
-      <c r="R32" s="12">
-        <f>Q32*M32</f>
+      <c r="T32" s="11">
+        <f>S32*M32</f>
         <v>1.714</v>
       </c>
-      <c r="S32" s="5"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="11"/>
+      <c r="X32" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="5"/>
     </row>
-    <row r="33" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
-        <f t="shared" si="1"/>
+    <row r="33" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>140</v>
+      <c r="B33" s="35"/>
+      <c r="C33" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="I33" s="5"/>
-      <c r="J33" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="K33" s="9">
+      <c r="J33" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="K33" s="8">
         <v>100</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="9">
         <v>8</v>
       </c>
       <c r="M33" s="5">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N33" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O33" s="11">
+      <c r="N33" s="43">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="O33" s="43">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+      <c r="P33" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q33" s="10">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="P33" s="12">
-        <f t="shared" si="7"/>
+      <c r="R33" s="11">
+        <f t="shared" si="11"/>
         <v>0.22</v>
       </c>
-      <c r="Q33" s="11">
+      <c r="S33" s="10">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="R33" s="12">
-        <f t="shared" ref="R33:R40" si="8">Q33*K33</f>
+      <c r="T33" s="11">
+        <f t="shared" ref="T33:T40" si="12">S33*K33</f>
         <v>0.22</v>
       </c>
-      <c r="S33" s="5"/>
+      <c r="U33" s="11"/>
+      <c r="V33" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="11"/>
+      <c r="X33" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="5"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
-        <f t="shared" si="1"/>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>144</v>
+      <c r="B34" s="35"/>
+      <c r="C34" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="I34" s="5"/>
-      <c r="J34" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="K34" s="9">
+      <c r="J34" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="K34" s="8">
         <v>50</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L34" s="9">
         <v>1</v>
       </c>
       <c r="M34" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N34" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O34" s="11">
+      <c r="N34" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O34" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P34" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q34" s="10">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="P34" s="12">
-        <f t="shared" si="7"/>
+      <c r="R34" s="11">
+        <f t="shared" si="11"/>
         <v>0.46499999999999997</v>
       </c>
-      <c r="Q34" s="11">
+      <c r="S34" s="10">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="R34" s="12">
-        <f t="shared" si="8"/>
+      <c r="T34" s="11">
+        <f t="shared" si="12"/>
         <v>0.46499999999999997</v>
       </c>
-      <c r="S34" s="5"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="11"/>
+      <c r="X34" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="5"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
-        <f t="shared" si="1"/>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="B35" s="37"/>
-      <c r="C35" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>148</v>
+      <c r="B35" s="35"/>
+      <c r="C35" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="I35" s="5"/>
-      <c r="J35" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="K35" s="9">
+      <c r="J35" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="K35" s="8">
         <v>100</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35" s="9">
         <v>1</v>
       </c>
       <c r="M35" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N35" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O35" s="11">
+      <c r="N35" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O35" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P35" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q35" s="10">
         <v>2E-3</v>
       </c>
-      <c r="P35" s="12">
-        <f t="shared" si="7"/>
+      <c r="R35" s="11">
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
-      <c r="Q35" s="11">
+      <c r="S35" s="10">
         <v>2E-3</v>
       </c>
-      <c r="R35" s="12">
-        <f t="shared" si="8"/>
+      <c r="T35" s="11">
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="S35" s="5"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="11"/>
+      <c r="X35" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="5"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
-        <f t="shared" si="1"/>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
-      <c r="B36" s="37"/>
-      <c r="C36" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>152</v>
+      <c r="B36" s="35"/>
+      <c r="C36" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="I36" s="5"/>
-      <c r="J36" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K36" s="9">
+      <c r="J36" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="K36" s="8">
         <v>50</v>
       </c>
-      <c r="L36" s="10">
+      <c r="L36" s="9">
         <v>1</v>
       </c>
       <c r="M36" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N36" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O36" s="11">
+      <c r="N36" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O36" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P36" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q36" s="10">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="P36" s="12">
-        <f t="shared" si="7"/>
+      <c r="R36" s="11">
+        <f t="shared" si="11"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="Q36" s="11">
+      <c r="S36" s="10">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="R36" s="12">
-        <f t="shared" si="8"/>
+      <c r="T36" s="11">
+        <f t="shared" si="12"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="S36" s="5"/>
+      <c r="U36" s="11"/>
+      <c r="V36" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="11"/>
+      <c r="X36" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="5"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
-        <f t="shared" si="1"/>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="B37" s="37"/>
-      <c r="C37" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>156</v>
+      <c r="B37" s="35"/>
+      <c r="C37" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>150</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="I37" s="5"/>
-      <c r="J37" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="K37" s="9">
+      <c r="J37" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="K37" s="8">
         <v>100</v>
       </c>
-      <c r="L37" s="10">
+      <c r="L37" s="9">
         <v>1</v>
       </c>
       <c r="M37" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N37" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O37" s="11">
+      <c r="N37" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O37" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P37" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q37" s="10">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="P37" s="12">
-        <f t="shared" si="7"/>
+      <c r="R37" s="11">
+        <f t="shared" si="11"/>
         <v>0.21</v>
       </c>
-      <c r="Q37" s="11">
+      <c r="S37" s="10">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="R37" s="12">
-        <f t="shared" si="8"/>
+      <c r="T37" s="11">
+        <f t="shared" si="12"/>
         <v>0.21</v>
       </c>
-      <c r="S37" s="5"/>
+      <c r="U37" s="11"/>
+      <c r="V37" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="11"/>
+      <c r="X37" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="5"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
-        <f t="shared" si="1"/>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="B38" s="37"/>
-      <c r="C38" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>160</v>
+      <c r="B38" s="35"/>
+      <c r="C38" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>154</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="I38" s="5"/>
-      <c r="J38" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="K38" s="9">
+      <c r="J38" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="K38" s="8">
         <v>100</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38" s="9">
         <v>1</v>
       </c>
       <c r="M38" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N38" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O38" s="11">
+      <c r="N38" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O38" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P38" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q38" s="10">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="P38" s="12">
-        <f t="shared" si="7"/>
+      <c r="R38" s="11">
+        <f t="shared" si="11"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="Q38" s="11">
+      <c r="S38" s="10">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="R38" s="12">
-        <f t="shared" si="8"/>
+      <c r="T38" s="11">
+        <f t="shared" si="12"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="S38" s="5"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W38" s="11"/>
+      <c r="X38" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="5"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
-        <f t="shared" si="1"/>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
-      <c r="B39" s="37"/>
-      <c r="C39" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>164</v>
+      <c r="B39" s="35"/>
+      <c r="C39" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="I39" s="5"/>
-      <c r="J39" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="K39" s="9">
+      <c r="J39" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="K39" s="8">
         <v>100</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="9">
         <v>1</v>
       </c>
       <c r="M39" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N39" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O39" s="11">
+      <c r="N39" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O39" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P39" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q39" s="10">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="P39" s="12">
-        <f t="shared" si="7"/>
+      <c r="R39" s="11">
+        <f t="shared" si="11"/>
         <v>0.26</v>
       </c>
-      <c r="Q39" s="11">
+      <c r="S39" s="10">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="R39" s="12">
-        <f t="shared" si="8"/>
+      <c r="T39" s="11">
+        <f t="shared" si="12"/>
         <v>0.26</v>
       </c>
-      <c r="S39" s="5"/>
+      <c r="U39" s="11"/>
+      <c r="V39" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="11"/>
+      <c r="X39" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="5"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
-        <f t="shared" si="1"/>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="B40" s="38"/>
-      <c r="C40" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>168</v>
+      <c r="B40" s="36"/>
+      <c r="C40" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>162</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>308</v>
+        <v>223</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="I40" s="5"/>
-      <c r="J40" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="K40" s="9">
+      <c r="J40" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="K40" s="8">
         <v>100</v>
       </c>
-      <c r="L40" s="10">
+      <c r="L40" s="9">
         <v>1</v>
       </c>
       <c r="M40" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N40" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O40" s="11">
+      <c r="N40" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O40" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P40" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q40" s="10">
         <v>2E-3</v>
       </c>
-      <c r="P40" s="12">
-        <f t="shared" si="7"/>
+      <c r="R40" s="11">
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
-      <c r="Q40" s="11">
+      <c r="S40" s="10">
         <v>2E-3</v>
       </c>
-      <c r="R40" s="12">
-        <f t="shared" si="8"/>
+      <c r="T40" s="11">
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="S40" s="5"/>
+      <c r="U40" s="11"/>
+      <c r="V40" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="11"/>
+      <c r="X40" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="5"/>
     </row>
-    <row r="41" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
-        <f t="shared" si="1"/>
+    <row r="41" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
-      <c r="B41" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>172</v>
+      <c r="B41" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>166</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
-      <c r="J41" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="K41" s="9">
+      <c r="J41" s="8"/>
+      <c r="K41" s="8">
         <v>50</v>
       </c>
-      <c r="L41" s="10">
+      <c r="L41" s="9">
         <v>1</v>
       </c>
       <c r="M41" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N41" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="O41" s="11">
+      <c r="N41" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O41" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P41" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q41" s="10">
         <v>1.8</v>
       </c>
-      <c r="P41" s="12">
-        <f>O41*L41</f>
+      <c r="R41" s="11">
+        <f>Q41*L41</f>
         <v>1.8</v>
       </c>
-      <c r="Q41" s="11">
+      <c r="S41" s="10">
         <v>1.8</v>
       </c>
-      <c r="R41" s="12">
+      <c r="T41" s="11">
         <v>1.8</v>
       </c>
-      <c r="S41" s="5"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="11"/>
+      <c r="X41" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="5"/>
     </row>
-    <row r="42" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
-        <f t="shared" si="1"/>
+    <row r="42" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>175</v>
+      <c r="B42" s="36"/>
+      <c r="C42" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D42" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>169</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="I42" s="5"/>
-      <c r="J42" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="K42" s="9">
+      <c r="J42" s="8"/>
+      <c r="K42" s="8">
         <v>1</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="9">
         <v>2</v>
       </c>
       <c r="M42" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N42" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O42" s="11">
+      <c r="N42" s="43">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="O42" s="43">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="P42" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q42" s="10">
         <v>0.28860000000000002</v>
       </c>
-      <c r="P42" s="12">
+      <c r="R42" s="11">
+        <f t="shared" si="7"/>
+        <v>0.57720000000000005</v>
+      </c>
+      <c r="S42" s="10">
+        <v>0.20930000000000001</v>
+      </c>
+      <c r="T42" s="11">
+        <f>S42*M42</f>
+        <v>2.093</v>
+      </c>
+      <c r="U42" s="11"/>
+      <c r="V42" s="46">
         <f t="shared" si="3"/>
-        <v>0.57720000000000005</v>
-      </c>
-      <c r="Q42" s="11">
-        <v>0.20930000000000001</v>
-      </c>
-      <c r="R42" s="12">
-        <f>Q42*M42</f>
-        <v>2.093</v>
-      </c>
-      <c r="S42" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="W42" s="11"/>
+      <c r="X42" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="5"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43" s="8">
-        <f t="shared" si="1"/>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <f t="shared" si="5"/>
         <v>41</v>
       </c>
-      <c r="B43" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>178</v>
+      <c r="B43" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="54" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>172</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="I43" s="5"/>
-      <c r="J43" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="K43" s="9">
+      <c r="J43" s="8"/>
+      <c r="K43" s="8">
         <v>1</v>
       </c>
-      <c r="L43" s="10">
+      <c r="L43" s="9">
         <v>1</v>
       </c>
       <c r="M43" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N43" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O43" s="11">
+      <c r="N43" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O43" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P43" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q43" s="10">
         <v>0.18729999999999999</v>
       </c>
-      <c r="P43" s="12">
+      <c r="R43" s="11">
+        <f t="shared" si="7"/>
+        <v>0.18729999999999999</v>
+      </c>
+      <c r="S43" s="10">
+        <v>0.18729999999999999</v>
+      </c>
+      <c r="T43" s="11">
+        <f t="shared" si="6"/>
+        <v>0.9365</v>
+      </c>
+      <c r="U43" s="56"/>
+      <c r="V43" s="46">
         <f t="shared" si="3"/>
-        <v>0.18729999999999999</v>
-      </c>
-      <c r="Q43" s="11">
-        <v>0.18729999999999999</v>
-      </c>
-      <c r="R43" s="12">
-        <f t="shared" si="2"/>
-        <v>0.9365</v>
+        <v>0</v>
+      </c>
+      <c r="W43" s="56"/>
+      <c r="X43" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44" s="8">
-        <f t="shared" si="1"/>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <f t="shared" si="5"/>
         <v>42</v>
       </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>182</v>
+      <c r="B44" s="35"/>
+      <c r="C44" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="I44" s="5"/>
-      <c r="J44" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="K44" s="9">
+      <c r="J44" s="8"/>
+      <c r="K44" s="8">
         <v>1</v>
       </c>
-      <c r="L44" s="10">
+      <c r="L44" s="9">
         <v>1</v>
       </c>
       <c r="M44" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N44" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O44" s="11">
+      <c r="N44" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O44" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P44" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q44" s="10">
         <v>0.3478</v>
       </c>
-      <c r="P44" s="12">
+      <c r="R44" s="11">
+        <f t="shared" si="7"/>
+        <v>0.3478</v>
+      </c>
+      <c r="S44" s="10">
+        <v>0.3478</v>
+      </c>
+      <c r="T44" s="11">
+        <f>S44*M44</f>
+        <v>1.7389999999999999</v>
+      </c>
+      <c r="U44" s="11"/>
+      <c r="V44" s="46">
         <f t="shared" si="3"/>
-        <v>0.3478</v>
-      </c>
-      <c r="Q44" s="11">
-        <v>0.3478</v>
-      </c>
-      <c r="R44" s="12">
-        <f>Q44*M44</f>
-        <v>1.7389999999999999</v>
-      </c>
-      <c r="S44" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="W44" s="11"/>
+      <c r="X44" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="5"/>
     </row>
-    <row r="45" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
-        <f t="shared" si="1"/>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <f t="shared" si="5"/>
         <v>43</v>
       </c>
-      <c r="B45" s="37"/>
-      <c r="C45" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>186</v>
+      <c r="B45" s="35"/>
+      <c r="C45" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="I45" s="5"/>
-      <c r="J45" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="K45" s="9">
+      <c r="J45" s="8"/>
+      <c r="K45" s="8">
         <v>1</v>
       </c>
-      <c r="L45" s="10">
+      <c r="L45" s="9">
         <v>1</v>
       </c>
       <c r="M45" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N45" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O45" s="11">
+      <c r="N45" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O45" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P45" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q45" s="10">
         <v>1.5923</v>
       </c>
-      <c r="P45" s="12">
+      <c r="R45" s="11">
+        <f t="shared" si="7"/>
+        <v>1.5923</v>
+      </c>
+      <c r="S45" s="10">
+        <v>1.5923</v>
+      </c>
+      <c r="T45" s="11">
+        <f t="shared" si="6"/>
+        <v>7.9615</v>
+      </c>
+      <c r="U45" s="11"/>
+      <c r="V45" s="46">
         <f t="shared" si="3"/>
-        <v>1.5923</v>
-      </c>
-      <c r="Q45" s="11">
-        <v>1.5923</v>
-      </c>
-      <c r="R45" s="12">
-        <f t="shared" si="2"/>
-        <v>7.9615</v>
-      </c>
-      <c r="S45" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="W45" s="11"/>
+      <c r="X45" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="5"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46" s="8">
-        <f t="shared" si="1"/>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>190</v>
+      <c r="B46" s="35"/>
+      <c r="C46" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D46" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>184</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
-      <c r="J46" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="K46" s="9">
+      <c r="J46" s="8"/>
+      <c r="K46" s="8">
         <v>1</v>
       </c>
-      <c r="L46" s="10">
+      <c r="L46" s="9">
         <v>1</v>
       </c>
       <c r="M46" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N46" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="O46" s="11">
+      <c r="N46" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O46" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P46" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q46" s="10">
         <v>0.34639999999999999</v>
       </c>
-      <c r="P46" s="12">
+      <c r="R46" s="11">
+        <f t="shared" si="7"/>
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="S46" s="10">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="T46" s="11">
+        <f t="shared" si="6"/>
+        <v>1.732</v>
+      </c>
+      <c r="U46" s="11"/>
+      <c r="V46" s="46">
         <f t="shared" si="3"/>
-        <v>0.34639999999999999</v>
-      </c>
-      <c r="Q46" s="11">
-        <v>0.34639999999999999</v>
-      </c>
-      <c r="R46" s="12">
-        <f t="shared" si="2"/>
-        <v>1.732</v>
-      </c>
-      <c r="S46" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="W46" s="11"/>
+      <c r="X46" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="5"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="8">
-        <f t="shared" si="1"/>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="B47" s="37"/>
-      <c r="C47" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>194</v>
+      <c r="B47" s="35"/>
+      <c r="C47" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="I47" s="5"/>
-      <c r="J47" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="K47" s="9">
+      <c r="J47" s="8"/>
+      <c r="K47" s="8">
         <v>1</v>
       </c>
-      <c r="L47" s="10">
+      <c r="L47" s="9">
         <v>1</v>
       </c>
       <c r="M47" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N47" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O47" s="11">
+      <c r="N47" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O47" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P47" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q47" s="10">
         <v>0.30620000000000003</v>
       </c>
-      <c r="P47" s="12">
+      <c r="R47" s="11">
+        <f t="shared" si="7"/>
+        <v>0.30620000000000003</v>
+      </c>
+      <c r="S47" s="10">
+        <v>0.30620000000000003</v>
+      </c>
+      <c r="T47" s="11">
+        <f t="shared" si="6"/>
+        <v>1.5310000000000001</v>
+      </c>
+      <c r="U47" s="11"/>
+      <c r="V47" s="46">
         <f t="shared" si="3"/>
-        <v>0.30620000000000003</v>
-      </c>
-      <c r="Q47" s="11">
-        <v>0.30620000000000003</v>
-      </c>
-      <c r="R47" s="12">
-        <f t="shared" si="2"/>
-        <v>1.5310000000000001</v>
-      </c>
-      <c r="S47" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="11"/>
+      <c r="X47" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="5"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
-        <f t="shared" si="1"/>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>198</v>
+      <c r="B48" s="35"/>
+      <c r="C48" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D48" s="54" t="s">
+        <v>194</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
-      <c r="J48" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K48" s="9">
+      <c r="J48" s="8"/>
+      <c r="K48" s="8">
         <v>2</v>
       </c>
-      <c r="L48" s="10">
+      <c r="L48" s="9">
         <v>1</v>
       </c>
       <c r="M48" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N48" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="O48" s="11">
+      <c r="N48" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O48" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P48" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q48" s="10">
         <f>16.15/2</f>
         <v>8.0749999999999993</v>
       </c>
-      <c r="P48" s="12">
-        <f>O48*K48</f>
+      <c r="R48" s="11">
+        <f>Q48*K48</f>
         <v>16.149999999999999</v>
       </c>
-      <c r="Q48" s="11">
+      <c r="S48" s="10">
         <f>37.05/5</f>
         <v>7.4099999999999993</v>
       </c>
-      <c r="R48" s="12">
-        <f t="shared" si="2"/>
+      <c r="T48" s="11">
+        <f t="shared" si="6"/>
         <v>37.049999999999997</v>
       </c>
-      <c r="S48" s="5"/>
+      <c r="U48" s="11"/>
+      <c r="V48" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W48" s="11"/>
+      <c r="X48" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="5"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
-        <f t="shared" si="1"/>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
-      <c r="B49" s="38"/>
-      <c r="C49" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>202</v>
+      <c r="B49" s="36"/>
+      <c r="C49" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>196</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
-      <c r="J49" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="K49" s="9">
+      <c r="J49" s="8"/>
+      <c r="K49" s="8">
         <v>1</v>
       </c>
-      <c r="L49" s="10">
+      <c r="L49" s="9">
         <v>1</v>
       </c>
       <c r="M49" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N49" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="O49" s="11">
+      <c r="N49" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O49" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P49" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q49" s="10">
         <v>1.92</v>
       </c>
-      <c r="P49" s="12">
+      <c r="R49" s="11">
+        <f t="shared" si="7"/>
+        <v>1.92</v>
+      </c>
+      <c r="S49" s="10">
+        <v>1.92</v>
+      </c>
+      <c r="T49" s="11">
+        <f t="shared" si="6"/>
+        <v>9.6</v>
+      </c>
+      <c r="U49" s="11"/>
+      <c r="V49" s="46">
         <f t="shared" si="3"/>
-        <v>1.92</v>
-      </c>
-      <c r="Q49" s="11">
-        <v>1.92</v>
-      </c>
-      <c r="R49" s="12">
-        <f t="shared" si="2"/>
-        <v>9.6</v>
-      </c>
-      <c r="S49" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="W49" s="11"/>
+      <c r="X49" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="5"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="8">
-        <f t="shared" si="1"/>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="B50" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>74</v>
+      <c r="B50" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="I50" s="5"/>
-      <c r="J50" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K50" s="9">
+      <c r="J50" s="8"/>
+      <c r="K50" s="8">
         <v>1</v>
       </c>
-      <c r="L50" s="10">
+      <c r="L50" s="9">
         <v>1</v>
       </c>
       <c r="M50" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N50" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O50" s="11">
+      <c r="N50" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O50" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P50" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q50" s="10">
         <v>1.8448</v>
       </c>
-      <c r="P50" s="12">
+      <c r="R50" s="11">
+        <f t="shared" si="7"/>
+        <v>1.8448</v>
+      </c>
+      <c r="S50" s="10">
+        <v>1.8448</v>
+      </c>
+      <c r="T50" s="11">
+        <f t="shared" si="6"/>
+        <v>9.2240000000000002</v>
+      </c>
+      <c r="U50" s="11"/>
+      <c r="V50" s="46">
         <f t="shared" si="3"/>
-        <v>1.8448</v>
-      </c>
-      <c r="Q50" s="11">
-        <v>1.8448</v>
-      </c>
-      <c r="R50" s="12">
-        <f t="shared" si="2"/>
-        <v>9.2240000000000002</v>
-      </c>
-      <c r="S50" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="11"/>
+      <c r="X50" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="5"/>
     </row>
-    <row r="51" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
-        <f t="shared" si="1"/>
+    <row r="51" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>77</v>
+      <c r="B51" s="38"/>
+      <c r="C51" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="I51" s="5"/>
-      <c r="J51" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K51" s="9">
+      <c r="J51" s="8"/>
+      <c r="K51" s="8">
         <v>1</v>
       </c>
-      <c r="L51" s="10">
+      <c r="L51" s="9">
         <v>2</v>
       </c>
       <c r="M51" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N51" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O51" s="11">
-        <v>0.72860000000000003</v>
-      </c>
-      <c r="P51" s="12">
-        <f t="shared" si="3"/>
-        <v>1.4572000000000001</v>
-      </c>
-      <c r="Q51" s="11">
-        <v>0.72860000000000003</v>
-      </c>
-      <c r="R51" s="12">
-        <f t="shared" si="2"/>
-        <v>7.2860000000000005</v>
-      </c>
-      <c r="S51" s="5"/>
-    </row>
-    <row r="52" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="8">
+      <c r="N51" s="43">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>80</v>
+      <c r="O51" s="43">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="P51" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q51" s="10">
+        <v>0.72860000000000003</v>
+      </c>
+      <c r="R51" s="11">
+        <f t="shared" si="7"/>
+        <v>1.4572000000000001</v>
+      </c>
+      <c r="S51" s="10">
+        <v>0.72860000000000003</v>
+      </c>
+      <c r="T51" s="11">
+        <f t="shared" si="6"/>
+        <v>7.2860000000000005</v>
+      </c>
+      <c r="U51" s="11"/>
+      <c r="V51" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="11"/>
+      <c r="X51" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="5"/>
+    </row>
+    <row r="52" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="B52" s="38"/>
+      <c r="C52" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
-      <c r="J52" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="K52" s="9">
+      <c r="J52" s="8"/>
+      <c r="K52" s="8">
         <v>1</v>
       </c>
-      <c r="L52" s="10">
+      <c r="L52" s="9">
         <v>1</v>
       </c>
       <c r="M52" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N52" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="O52" s="11">
+      <c r="N52" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O52" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P52" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q52" s="10">
         <v>1.74</v>
       </c>
-      <c r="P52" s="12">
+      <c r="R52" s="11">
+        <f t="shared" si="7"/>
+        <v>1.74</v>
+      </c>
+      <c r="S52" s="10">
+        <v>1.74</v>
+      </c>
+      <c r="T52" s="11">
+        <f t="shared" si="6"/>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="U52" s="11"/>
+      <c r="V52" s="46">
         <f t="shared" si="3"/>
-        <v>1.74</v>
-      </c>
-      <c r="Q52" s="11">
-        <v>1.74</v>
-      </c>
-      <c r="R52" s="12">
-        <f t="shared" si="2"/>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="S52" s="5" t="s">
-        <v>321</v>
+        <v>0</v>
+      </c>
+      <c r="W52" s="11"/>
+      <c r="X52" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="5" t="s">
+        <v>308</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="8">
-        <f t="shared" si="1"/>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>83</v>
+      <c r="B53" s="38"/>
+      <c r="C53" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
-      <c r="J53" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K53" s="9">
+      <c r="J53" s="8"/>
+      <c r="K53" s="8">
         <v>10</v>
       </c>
-      <c r="L53" s="10">
+      <c r="L53" s="9">
         <v>1</v>
       </c>
       <c r="M53" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N53" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="O53" s="11">
+      <c r="N53" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O53" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P53" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q53" s="10">
         <v>4</v>
       </c>
-      <c r="P53" s="12">
-        <f>O53*L53</f>
+      <c r="R53" s="11">
+        <f>Q53*L53</f>
         <v>4</v>
       </c>
-      <c r="Q53" s="11">
+      <c r="S53" s="10">
         <v>4</v>
       </c>
-      <c r="R53" s="12">
+      <c r="T53" s="11">
         <v>4</v>
       </c>
-      <c r="S53" s="5"/>
+      <c r="U53" s="11"/>
+      <c r="V53" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W53" s="11"/>
+      <c r="X53" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y53" s="5"/>
     </row>
-    <row r="54" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="8">
-        <f t="shared" si="1"/>
+    <row r="54" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>96</v>
+      <c r="B54" s="38"/>
+      <c r="C54" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
-      <c r="J54" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="K54" s="9">
+      <c r="J54" s="8"/>
+      <c r="K54" s="8">
         <v>1</v>
       </c>
-      <c r="L54" s="10">
+      <c r="L54" s="9">
         <v>2</v>
       </c>
       <c r="M54" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N54" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="O54" s="11">
+      <c r="N54" s="43">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="O54" s="43">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="P54" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q54" s="10">
         <v>1.61</v>
       </c>
-      <c r="P54" s="12">
+      <c r="R54" s="11">
+        <f t="shared" si="7"/>
+        <v>3.22</v>
+      </c>
+      <c r="S54" s="10">
+        <v>1.61</v>
+      </c>
+      <c r="T54" s="11">
+        <f t="shared" si="6"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="U54" s="11"/>
+      <c r="V54" s="46">
         <f t="shared" si="3"/>
-        <v>3.22</v>
-      </c>
-      <c r="Q54" s="11">
-        <v>1.61</v>
-      </c>
-      <c r="R54" s="12">
-        <f t="shared" si="2"/>
-        <v>16.100000000000001</v>
-      </c>
-      <c r="S54" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="11"/>
+      <c r="X54" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="5"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A55" s="8">
-        <f t="shared" si="1"/>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>107</v>
+      <c r="B55" s="38"/>
+      <c r="C55" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>101</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
-      <c r="J55" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K55" s="9">
+      <c r="J55" s="8"/>
+      <c r="K55" s="8">
         <v>10</v>
       </c>
-      <c r="L55" s="10">
+      <c r="L55" s="9">
         <v>2</v>
       </c>
       <c r="M55" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N55" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="O55" s="11">
+      <c r="N55" s="43">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="O55" s="43">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="P55" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q55" s="10">
         <v>0.19</v>
       </c>
-      <c r="P55" s="11">
+      <c r="R55" s="10">
         <v>0.19</v>
       </c>
-      <c r="Q55" s="11">
+      <c r="S55" s="10">
         <v>0.19</v>
       </c>
-      <c r="R55" s="11">
+      <c r="T55" s="10">
         <v>0.19</v>
       </c>
+      <c r="U55" s="57"/>
+      <c r="V55" s="46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W55" s="57"/>
+      <c r="X55" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56" s="8">
-        <f t="shared" si="1"/>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="F56" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="17">
+      <c r="B56" s="38"/>
+      <c r="C56" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="16">
         <v>4</v>
       </c>
-      <c r="M56" s="17">
+      <c r="M56" s="16">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="18">
-        <f t="shared" ref="P56:P57" si="9">O56*L56</f>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="19"/>
-      <c r="R56" s="18">
-        <f>Q56*M56</f>
-        <v>0</v>
-      </c>
-      <c r="S56" s="17"/>
+      <c r="N56" s="43">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="O56" s="43">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="16"/>
+      <c r="R56" s="17">
+        <f t="shared" ref="R56:R57" si="13">Q56*L56</f>
+        <v>0</v>
+      </c>
+      <c r="S56" s="18"/>
+      <c r="T56" s="17">
+        <f>S56*M56</f>
+        <v>0</v>
+      </c>
+      <c r="U56" s="17"/>
+      <c r="V56" s="17">
+        <f>U56*N56</f>
+        <v>0</v>
+      </c>
+      <c r="W56" s="17"/>
+      <c r="X56" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y56" s="16"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="F57" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="17">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="B57" s="38"/>
+      <c r="C57" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="16">
         <v>1</v>
       </c>
-      <c r="M57" s="17">
+      <c r="M57" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="19"/>
-      <c r="R57" s="18">
-        <f>Q57*M57</f>
-        <v>0</v>
-      </c>
-      <c r="S57" s="17"/>
+      <c r="N57" s="43">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="O57" s="43">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="P57" s="16"/>
+      <c r="Q57" s="16"/>
+      <c r="R57" s="17">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="18"/>
+      <c r="T57" s="17">
+        <f>S57*M57</f>
+        <v>0</v>
+      </c>
+      <c r="U57" s="17"/>
+      <c r="V57" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W57" s="17"/>
+      <c r="X57" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y57" s="16"/>
     </row>
-    <row r="58" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="N58" s="24"/>
-      <c r="O58" s="25"/>
-      <c r="P58" s="26">
-        <f>SUM(P3:P55)</f>
-        <v>73.677199999999985</v>
-      </c>
+    <row r="58" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="N58" s="23"/>
+      <c r="O58" s="23"/>
+      <c r="P58" s="23"/>
       <c r="Q58" s="24"/>
-      <c r="R58" s="27">
+      <c r="R58" s="25">
         <f>SUM(R3:R55)</f>
-        <v>248.25749999999994</v>
-      </c>
+        <v>73.678699999999992</v>
+      </c>
+      <c r="S58" s="23"/>
+      <c r="T58" s="26">
+        <f>SUM(T3:T55)</f>
+        <v>248.25999999999993</v>
+      </c>
+      <c r="U58" s="26"/>
+      <c r="V58" s="26"/>
+      <c r="W58" s="26"/>
+      <c r="X58" s="26"/>
     </row>
-    <row r="59" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:S1"/>
+  <mergeCells count="7">
+    <mergeCell ref="B50:B57"/>
+    <mergeCell ref="A1:Y1"/>
     <mergeCell ref="B3:B18"/>
     <mergeCell ref="B19:B23"/>
     <mergeCell ref="B41:B42"/>
@@ -4869,7 +6141,7 @@
     <mergeCell ref="B27:B40"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
-  <conditionalFormatting sqref="P3:P54 P56:P57">
+  <conditionalFormatting sqref="R3:R54 R56:R57">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -4883,7 +6155,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:M57">
+  <conditionalFormatting sqref="L3:O57">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -4895,7 +6167,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R54 R56:R57">
+  <conditionalFormatting sqref="T3:X3 T4:U54 W4:W54 T56:X57 X4:X57 V4:V55">
     <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
@@ -4910,58 +6182,58 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N3" r:id="rId1" xr:uid="{FEF0640F-70F9-47AE-873C-5E777EAAABF3}"/>
-    <hyperlink ref="N4" r:id="rId2" xr:uid="{E42AE065-4F16-486E-AB87-4BD63AA9CC3D}"/>
-    <hyperlink ref="N5" r:id="rId3" xr:uid="{9B000C1C-2E43-4275-9029-6FD743822061}"/>
-    <hyperlink ref="N6" r:id="rId4" xr:uid="{393E845A-FE37-4AEC-96E1-3A30841E03C4}"/>
-    <hyperlink ref="N7" r:id="rId5" xr:uid="{AE50644F-F482-4F60-8EAF-3161F32493E9}"/>
-    <hyperlink ref="N8" r:id="rId6" xr:uid="{72549220-D453-467C-8D49-02901880B1D9}"/>
-    <hyperlink ref="N9" r:id="rId7" xr:uid="{FB4B371C-3C21-4960-9E99-AFFFCB427483}"/>
-    <hyperlink ref="N10" r:id="rId8" xr:uid="{540CCC4D-F3EC-488C-B987-D637FE7218DD}"/>
-    <hyperlink ref="N11" r:id="rId9" xr:uid="{33E3B06A-073D-4C7F-BCE0-E14B13DE6FEC}"/>
-    <hyperlink ref="N12" r:id="rId10" xr:uid="{0B4DD2A5-C52A-4412-9F0D-BEF11CECCA3A}"/>
-    <hyperlink ref="N13" r:id="rId11" xr:uid="{B2CC03B9-5DC9-41E0-BF09-65C7BE8F51C3}"/>
-    <hyperlink ref="N14" r:id="rId12" xr:uid="{5CB80D63-3320-4FFB-BDB3-87B5E9BB1D14}"/>
-    <hyperlink ref="N15" r:id="rId13" xr:uid="{E9DF8242-F527-4FAB-A56E-1D71C3244AC7}"/>
-    <hyperlink ref="N16" r:id="rId14" xr:uid="{F3B0F722-6B42-4B90-A021-DF1065BA7EB1}"/>
-    <hyperlink ref="N17" r:id="rId15" xr:uid="{1EC0E00D-6B99-4269-9086-CD681A3E9BEF}"/>
-    <hyperlink ref="N18" r:id="rId16" xr:uid="{F089ED1C-B5A0-49A1-92F7-83B0E7BE489D}"/>
-    <hyperlink ref="N19" r:id="rId17" xr:uid="{05AE4DA0-8828-4EB1-8ECC-61EC98D8116A}"/>
-    <hyperlink ref="N20" r:id="rId18" xr:uid="{D29066AD-06A7-4BDC-B822-CA97C4828F23}"/>
-    <hyperlink ref="N21" r:id="rId19" xr:uid="{EB738F35-73EB-497E-973E-95236673585F}"/>
-    <hyperlink ref="N22" r:id="rId20" xr:uid="{DF06AD6E-62EA-46CF-847F-3790BCF991C8}"/>
-    <hyperlink ref="N23" r:id="rId21" xr:uid="{572BE3A9-AF7F-4452-B27C-2557C692B7F5}"/>
-    <hyperlink ref="N24" r:id="rId22" xr:uid="{F50D2F81-9954-46E2-ADEE-43550BB332F5}"/>
-    <hyperlink ref="N25" r:id="rId23" xr:uid="{EA4F5CD5-4D3D-4250-A05A-1BB71AFA270F}"/>
-    <hyperlink ref="N26" r:id="rId24" xr:uid="{65AF0AC5-3BB9-41C4-9A7A-9A29F175BDA3}"/>
-    <hyperlink ref="N27" r:id="rId25" xr:uid="{D51FC6A8-4CCD-4DC5-B867-1BF40AF81FAC}"/>
-    <hyperlink ref="N28" r:id="rId26" xr:uid="{5EA4EF54-C3D0-498C-BE8E-7FA27A9AC1B6}"/>
-    <hyperlink ref="N29" r:id="rId27" xr:uid="{68B44140-277C-4409-ADCE-3069C6251AE1}"/>
-    <hyperlink ref="N30" r:id="rId28" xr:uid="{FD3C9FC6-3957-4848-BF50-D0F1CCC629AC}"/>
-    <hyperlink ref="N31" r:id="rId29" xr:uid="{EE50FD3F-D71A-4F72-AF03-CE1B95D14127}"/>
-    <hyperlink ref="N32" r:id="rId30" xr:uid="{A33622CD-0F8B-487A-829D-91E6B7E3E834}"/>
-    <hyperlink ref="N33" r:id="rId31" xr:uid="{6DAE296B-AE93-4D94-BDA0-26DEA532A9DC}"/>
-    <hyperlink ref="N34" r:id="rId32" xr:uid="{EE601309-4ADE-468E-A406-EBE4B821AA59}"/>
-    <hyperlink ref="N35" r:id="rId33" xr:uid="{610B3EE9-2DD0-480F-B16F-BF17FB82CED9}"/>
-    <hyperlink ref="N36" r:id="rId34" xr:uid="{8E232D8B-888C-4B8D-91D5-6F6022AFCFB9}"/>
-    <hyperlink ref="N37" r:id="rId35" xr:uid="{9BD68064-1E42-44E2-8858-E8219FEA6ADE}"/>
-    <hyperlink ref="N38" r:id="rId36" xr:uid="{677C7315-C594-4492-B57C-1C5D505DB5EB}"/>
-    <hyperlink ref="N39" r:id="rId37" xr:uid="{88F1F464-34A4-4D28-86C3-C3F864637EFA}"/>
-    <hyperlink ref="N40" r:id="rId38" xr:uid="{04916259-62EA-42B4-A38E-0B8CB58383AC}"/>
-    <hyperlink ref="N42" r:id="rId39" xr:uid="{56F92723-72F0-401F-8F4F-53F7C34DB375}"/>
-    <hyperlink ref="N43" r:id="rId40" xr:uid="{B5349DF3-41CA-431B-9038-750DFDFFEA62}"/>
-    <hyperlink ref="N44" r:id="rId41" xr:uid="{39DF180C-F53B-4059-A422-135A559DB4EA}"/>
-    <hyperlink ref="N45" r:id="rId42" xr:uid="{8B3FEE46-DBED-4B6D-8227-4D5825CA24F2}"/>
-    <hyperlink ref="N46" r:id="rId43" xr:uid="{FDBD0A15-A013-4A34-970B-CE89D9D7ABA6}"/>
-    <hyperlink ref="N47" r:id="rId44" xr:uid="{F506133E-6FD1-40B0-A371-3D473223A507}"/>
-    <hyperlink ref="N49" r:id="rId45" xr:uid="{B0DD232C-EE20-4F71-8CCE-8F189BBCAE31}"/>
-    <hyperlink ref="N50" r:id="rId46" xr:uid="{596E859F-3C1A-488D-8C6C-3B8F0C163E26}"/>
-    <hyperlink ref="N51" r:id="rId47" xr:uid="{20EC973F-ABEE-4522-A536-3C9043FC0933}"/>
-    <hyperlink ref="N54" r:id="rId48" display="LCSC" xr:uid="{340CB9D3-417A-4840-9FDD-D2D28278EF5B}"/>
-    <hyperlink ref="N55" r:id="rId49" xr:uid="{AABF823B-413E-4EC2-B954-DF074731CAA7}"/>
-    <hyperlink ref="N48" r:id="rId50" xr:uid="{1114458F-A78D-4A76-B1CF-305337F52263}"/>
-    <hyperlink ref="N53" r:id="rId51" xr:uid="{1E96E8EA-3806-41F4-BDB9-DF5C3FCF6928}"/>
-    <hyperlink ref="N41" r:id="rId52" xr:uid="{2F6C76CB-7AFF-4E6D-9732-3183EF2507E8}"/>
+    <hyperlink ref="P3" r:id="rId1" xr:uid="{FEF0640F-70F9-47AE-873C-5E777EAAABF3}"/>
+    <hyperlink ref="P4" r:id="rId2" xr:uid="{E42AE065-4F16-486E-AB87-4BD63AA9CC3D}"/>
+    <hyperlink ref="P5" r:id="rId3" xr:uid="{9B000C1C-2E43-4275-9029-6FD743822061}"/>
+    <hyperlink ref="P6" r:id="rId4" xr:uid="{393E845A-FE37-4AEC-96E1-3A30841E03C4}"/>
+    <hyperlink ref="P7" r:id="rId5" xr:uid="{AE50644F-F482-4F60-8EAF-3161F32493E9}"/>
+    <hyperlink ref="P8" r:id="rId6" xr:uid="{72549220-D453-467C-8D49-02901880B1D9}"/>
+    <hyperlink ref="P9" r:id="rId7" xr:uid="{FB4B371C-3C21-4960-9E99-AFFFCB427483}"/>
+    <hyperlink ref="P10" r:id="rId8" xr:uid="{540CCC4D-F3EC-488C-B987-D637FE7218DD}"/>
+    <hyperlink ref="P11" r:id="rId9" xr:uid="{33E3B06A-073D-4C7F-BCE0-E14B13DE6FEC}"/>
+    <hyperlink ref="P12" r:id="rId10" xr:uid="{0B4DD2A5-C52A-4412-9F0D-BEF11CECCA3A}"/>
+    <hyperlink ref="P13" r:id="rId11" xr:uid="{B2CC03B9-5DC9-41E0-BF09-65C7BE8F51C3}"/>
+    <hyperlink ref="P14" r:id="rId12" xr:uid="{5CB80D63-3320-4FFB-BDB3-87B5E9BB1D14}"/>
+    <hyperlink ref="P15" r:id="rId13" xr:uid="{E9DF8242-F527-4FAB-A56E-1D71C3244AC7}"/>
+    <hyperlink ref="P16" r:id="rId14" xr:uid="{F3B0F722-6B42-4B90-A021-DF1065BA7EB1}"/>
+    <hyperlink ref="P18" r:id="rId15" xr:uid="{F089ED1C-B5A0-49A1-92F7-83B0E7BE489D}"/>
+    <hyperlink ref="P19" r:id="rId16" xr:uid="{05AE4DA0-8828-4EB1-8ECC-61EC98D8116A}"/>
+    <hyperlink ref="P20" r:id="rId17" xr:uid="{D29066AD-06A7-4BDC-B822-CA97C4828F23}"/>
+    <hyperlink ref="P21" r:id="rId18" xr:uid="{EB738F35-73EB-497E-973E-95236673585F}"/>
+    <hyperlink ref="P22" r:id="rId19" xr:uid="{DF06AD6E-62EA-46CF-847F-3790BCF991C8}"/>
+    <hyperlink ref="P23" r:id="rId20" xr:uid="{572BE3A9-AF7F-4452-B27C-2557C692B7F5}"/>
+    <hyperlink ref="P24" r:id="rId21" xr:uid="{F50D2F81-9954-46E2-ADEE-43550BB332F5}"/>
+    <hyperlink ref="P25" r:id="rId22" xr:uid="{EA4F5CD5-4D3D-4250-A05A-1BB71AFA270F}"/>
+    <hyperlink ref="P26" r:id="rId23" xr:uid="{65AF0AC5-3BB9-41C4-9A7A-9A29F175BDA3}"/>
+    <hyperlink ref="P27" r:id="rId24" xr:uid="{D51FC6A8-4CCD-4DC5-B867-1BF40AF81FAC}"/>
+    <hyperlink ref="P28" r:id="rId25" xr:uid="{5EA4EF54-C3D0-498C-BE8E-7FA27A9AC1B6}"/>
+    <hyperlink ref="P29" r:id="rId26" xr:uid="{68B44140-277C-4409-ADCE-3069C6251AE1}"/>
+    <hyperlink ref="P30" r:id="rId27" xr:uid="{FD3C9FC6-3957-4848-BF50-D0F1CCC629AC}"/>
+    <hyperlink ref="P31" r:id="rId28" xr:uid="{EE50FD3F-D71A-4F72-AF03-CE1B95D14127}"/>
+    <hyperlink ref="P32" r:id="rId29" xr:uid="{A33622CD-0F8B-487A-829D-91E6B7E3E834}"/>
+    <hyperlink ref="P33" r:id="rId30" xr:uid="{6DAE296B-AE93-4D94-BDA0-26DEA532A9DC}"/>
+    <hyperlink ref="P34" r:id="rId31" xr:uid="{EE601309-4ADE-468E-A406-EBE4B821AA59}"/>
+    <hyperlink ref="P35" r:id="rId32" xr:uid="{610B3EE9-2DD0-480F-B16F-BF17FB82CED9}"/>
+    <hyperlink ref="P36" r:id="rId33" xr:uid="{8E232D8B-888C-4B8D-91D5-6F6022AFCFB9}"/>
+    <hyperlink ref="P37" r:id="rId34" xr:uid="{9BD68064-1E42-44E2-8858-E8219FEA6ADE}"/>
+    <hyperlink ref="P38" r:id="rId35" xr:uid="{677C7315-C594-4492-B57C-1C5D505DB5EB}"/>
+    <hyperlink ref="P39" r:id="rId36" xr:uid="{88F1F464-34A4-4D28-86C3-C3F864637EFA}"/>
+    <hyperlink ref="P40" r:id="rId37" xr:uid="{04916259-62EA-42B4-A38E-0B8CB58383AC}"/>
+    <hyperlink ref="P42" r:id="rId38" xr:uid="{56F92723-72F0-401F-8F4F-53F7C34DB375}"/>
+    <hyperlink ref="P43" r:id="rId39" xr:uid="{B5349DF3-41CA-431B-9038-750DFDFFEA62}"/>
+    <hyperlink ref="P44" r:id="rId40" xr:uid="{39DF180C-F53B-4059-A422-135A559DB4EA}"/>
+    <hyperlink ref="P45" r:id="rId41" xr:uid="{8B3FEE46-DBED-4B6D-8227-4D5825CA24F2}"/>
+    <hyperlink ref="P46" r:id="rId42" xr:uid="{FDBD0A15-A013-4A34-970B-CE89D9D7ABA6}"/>
+    <hyperlink ref="P47" r:id="rId43" xr:uid="{F506133E-6FD1-40B0-A371-3D473223A507}"/>
+    <hyperlink ref="P49" r:id="rId44" xr:uid="{B0DD232C-EE20-4F71-8CCE-8F189BBCAE31}"/>
+    <hyperlink ref="P50" r:id="rId45" xr:uid="{596E859F-3C1A-488D-8C6C-3B8F0C163E26}"/>
+    <hyperlink ref="P51" r:id="rId46" xr:uid="{20EC973F-ABEE-4522-A536-3C9043FC0933}"/>
+    <hyperlink ref="P54" r:id="rId47" display="LCSC" xr:uid="{340CB9D3-417A-4840-9FDD-D2D28278EF5B}"/>
+    <hyperlink ref="P55" r:id="rId48" xr:uid="{AABF823B-413E-4EC2-B954-DF074731CAA7}"/>
+    <hyperlink ref="P48" r:id="rId49" xr:uid="{1114458F-A78D-4A76-B1CF-305337F52263}"/>
+    <hyperlink ref="P53" r:id="rId50" xr:uid="{1E96E8EA-3806-41F4-BDB9-DF5C3FCF6928}"/>
+    <hyperlink ref="P41" r:id="rId51" xr:uid="{2F6C76CB-7AFF-4E6D-9732-3183EF2507E8}"/>
+    <hyperlink ref="P17" r:id="rId52" xr:uid="{7635F356-1FFC-477A-B35F-196CE8E57DB4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId53"/>
@@ -4979,7 +6251,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P54 P56:P57</xm:sqref>
+          <xm:sqref>R3:R54 R56:R57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{19B0CB15-0C97-4D9D-B36B-BDCECB480ACD}">
@@ -4992,7 +6264,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R3:R54 R56:R57</xm:sqref>
+          <xm:sqref>T3:X3 T4:U54 W4:W54 T56:X57 X4:X57 V4:V55</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/SM_Top Board/_BOM/SM_Top_PCB_LCSC.xlsx
+++ b/Deliverables/SM_Top Board/_BOM/SM_Top_PCB_LCSC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20376"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Github\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08183F3-093D-4EEB-971F-D4617E5FCF17}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0BB217-F58E-4719-9D14-24D9F4223225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,13 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -951,9 +958,6 @@
     <t>Alexpress</t>
   </si>
   <si>
-    <t>Unable to find chinese supplier. Farnell has 11 parts in stock</t>
-  </si>
-  <si>
     <t>Local Supplier</t>
   </si>
   <si>
@@ -1021,6 +1025,9 @@
   </si>
   <si>
     <t>--------</t>
+  </si>
+  <si>
+    <t>quote by karen</t>
   </si>
 </sst>
 </file>
@@ -1447,33 +1454,6 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1541,6 +1521,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1853,203 +1860,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="55" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="57"/>
     </row>
     <row r="2" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="C2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="52" t="s">
+      <c r="C2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="I2" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="J2" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="38" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="L2" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="M2" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="O2" s="38" t="s">
         <v>315</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="P2" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="P2" s="47" t="s">
+      <c r="Q2" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="R2" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="S2" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="T2" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="U2" s="39" t="s">
+        <v>318</v>
+      </c>
+      <c r="V2" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="W2" s="39" t="s">
+        <v>320</v>
+      </c>
+      <c r="X2" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y2" s="40" t="s">
         <v>317</v>
-      </c>
-      <c r="Q2" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="R2" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="S2" s="48" t="s">
-        <v>211</v>
-      </c>
-      <c r="T2" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="U2" s="48" t="s">
-        <v>319</v>
-      </c>
-      <c r="V2" s="47" t="s">
-        <v>320</v>
-      </c>
-      <c r="W2" s="48" t="s">
-        <v>321</v>
-      </c>
-      <c r="X2" s="47" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y2" s="49" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
+      <c r="A3" s="30">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="58" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>311</v>
-      </c>
-      <c r="D3" s="53" t="s">
+      <c r="C3" s="31" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="F3" s="40" t="s">
+      <c r="E3" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="I3" s="41" t="s">
-        <v>323</v>
-      </c>
-      <c r="J3" s="40" t="s">
+      <c r="I3" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="J3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="40">
+      <c r="K3" s="31">
         <v>1</v>
       </c>
-      <c r="L3" s="42">
+      <c r="L3" s="33">
         <v>2</v>
       </c>
-      <c r="M3" s="43">
+      <c r="M3" s="34">
         <f>L3*5</f>
         <v>10</v>
       </c>
-      <c r="N3" s="43">
+      <c r="N3" s="34">
         <f>L3*25</f>
         <v>50</v>
       </c>
-      <c r="O3" s="43">
+      <c r="O3" s="34">
         <f>L3*100</f>
         <v>200</v>
       </c>
-      <c r="P3" s="44" t="s">
+      <c r="P3" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="Q3" s="45">
+      <c r="Q3" s="36">
         <v>0.25669999999999998</v>
       </c>
-      <c r="R3" s="46">
+      <c r="R3" s="37">
         <f>Q3*L3</f>
         <v>0.51339999999999997</v>
       </c>
-      <c r="S3" s="45">
+      <c r="S3" s="36">
         <v>0.19850000000000001</v>
       </c>
-      <c r="T3" s="46">
+      <c r="T3" s="37">
         <f>S3*M3</f>
         <v>1.9850000000000001</v>
       </c>
-      <c r="U3" s="46">
+      <c r="U3" s="37">
         <v>0.18790000000000001</v>
       </c>
-      <c r="V3" s="46">
+      <c r="V3" s="37">
         <f>U3*N3</f>
         <v>9.3950000000000014</v>
       </c>
-      <c r="W3" s="46">
+      <c r="W3" s="37">
         <v>0.1772</v>
       </c>
-      <c r="X3" s="46">
+      <c r="X3" s="37">
         <f>W3*O3</f>
         <v>35.44</v>
       </c>
-      <c r="Y3" s="43"/>
+      <c r="Y3" s="34"/>
     </row>
     <row r="4" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="33"/>
+      <c r="B4" s="59"/>
       <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="45" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -2064,8 +2071,8 @@
       <c r="H4" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="I4" s="41" t="s">
-        <v>323</v>
+      <c r="I4" s="32" t="s">
+        <v>322</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>6</v>
@@ -2080,11 +2087,11 @@
         <f t="shared" ref="M4:M57" si="0">L4*5</f>
         <v>40</v>
       </c>
-      <c r="N4" s="43">
+      <c r="N4" s="34">
         <f t="shared" ref="N4:N57" si="1">L4*25</f>
         <v>200</v>
       </c>
-      <c r="O4" s="43">
+      <c r="O4" s="34">
         <f t="shared" ref="O4:O57" si="2">L4*100</f>
         <v>800</v>
       </c>
@@ -2108,14 +2115,14 @@
       <c r="U4" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="V4" s="46">
+      <c r="V4" s="37">
         <f t="shared" ref="V4:V57" si="3">U4*N4</f>
         <v>0.8</v>
       </c>
       <c r="W4" s="11">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="X4" s="46">
+      <c r="X4" s="37">
         <f t="shared" ref="X4:X57" si="4">W4*O4</f>
         <v>2.48</v>
       </c>
@@ -2126,11 +2133,11 @@
         <f t="shared" ref="A5:A57" si="5">A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="59"/>
       <c r="C5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="45" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -2161,11 +2168,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -2189,14 +2196,14 @@
       <c r="U5" s="11">
         <v>0.1045</v>
       </c>
-      <c r="V5" s="46">
+      <c r="V5" s="37">
         <f t="shared" si="3"/>
         <v>2.6124999999999998</v>
       </c>
       <c r="W5" s="11">
         <v>8.3299999999999999E-2</v>
       </c>
-      <c r="X5" s="46">
+      <c r="X5" s="37">
         <f t="shared" si="4"/>
         <v>8.33</v>
       </c>
@@ -2209,15 +2216,15 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D6" s="54" t="s">
+        <v>311</v>
+      </c>
+      <c r="D6" s="45" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>18</v>
@@ -2229,7 +2236,7 @@
         <v>258</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
@@ -2244,11 +2251,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N6" s="43">
+      <c r="N6" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -2272,14 +2279,14 @@
       <c r="U6" s="11">
         <v>0.39140000000000003</v>
       </c>
-      <c r="V6" s="46">
+      <c r="V6" s="37">
         <f t="shared" si="3"/>
         <v>9.7850000000000001</v>
       </c>
       <c r="W6" s="11">
         <v>0.3553</v>
       </c>
-      <c r="X6" s="46">
+      <c r="X6" s="37">
         <f t="shared" si="4"/>
         <v>35.53</v>
       </c>
@@ -2290,15 +2297,15 @@
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D7" s="54" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>21</v>
@@ -2310,7 +2317,7 @@
         <v>259</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>19</v>
@@ -2325,10 +2332,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N7" s="43">
+      <c r="N7" s="34">
         <v>30</v>
       </c>
-      <c r="O7" s="43">
+      <c r="O7" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -2352,14 +2359,14 @@
       <c r="U7" s="11">
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="V7" s="46">
+      <c r="V7" s="37">
         <f t="shared" si="3"/>
         <v>2.133</v>
       </c>
       <c r="W7" s="11">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="X7" s="46">
+      <c r="X7" s="37">
         <f t="shared" si="4"/>
         <v>5.4</v>
       </c>
@@ -2370,11 +2377,11 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="45" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -2390,7 +2397,7 @@
         <v>260</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>22</v>
@@ -2405,11 +2412,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N8" s="43">
+      <c r="N8" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -2433,14 +2440,14 @@
       <c r="U8" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="V8" s="46">
+      <c r="V8" s="37">
         <f>U8*K8</f>
         <v>0.2</v>
       </c>
       <c r="W8" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="X8" s="46">
+      <c r="X8" s="37">
         <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
@@ -2451,11 +2458,11 @@
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="45" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="8" t="s">
@@ -2471,7 +2478,7 @@
         <v>261</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>26</v>
@@ -2486,10 +2493,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N9" s="43">
+      <c r="N9" s="34">
         <v>40</v>
       </c>
-      <c r="O9" s="43">
+      <c r="O9" s="34">
         <v>120</v>
       </c>
       <c r="P9" s="14" t="s">
@@ -2512,14 +2519,14 @@
       <c r="U9" s="11">
         <v>3.1199999999999999E-2</v>
       </c>
-      <c r="V9" s="46">
+      <c r="V9" s="37">
         <f t="shared" si="3"/>
         <v>1.248</v>
       </c>
       <c r="W9" s="11">
         <v>3.1199999999999999E-2</v>
       </c>
-      <c r="X9" s="46">
+      <c r="X9" s="37">
         <f t="shared" si="4"/>
         <v>3.7439999999999998</v>
       </c>
@@ -2530,11 +2537,11 @@
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="D10" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="D10" s="45" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -2550,7 +2557,7 @@
         <v>262</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>31</v>
@@ -2564,10 +2571,10 @@
       <c r="M10" s="5">
         <v>7</v>
       </c>
-      <c r="N10" s="43">
+      <c r="N10" s="34">
         <v>27</v>
       </c>
-      <c r="O10" s="43">
+      <c r="O10" s="34">
         <v>105</v>
       </c>
       <c r="P10" s="14" t="s">
@@ -2590,14 +2597,14 @@
       <c r="U10" s="11">
         <v>0.18920000000000001</v>
       </c>
-      <c r="V10" s="46">
+      <c r="V10" s="37">
         <f t="shared" si="3"/>
         <v>5.1084000000000005</v>
       </c>
       <c r="W10" s="11">
         <v>0.1633</v>
       </c>
-      <c r="X10" s="46">
+      <c r="X10" s="37">
         <f t="shared" si="4"/>
         <v>17.1465</v>
       </c>
@@ -2608,11 +2615,11 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="B11" s="33"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="45" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -2628,7 +2635,7 @@
         <v>263</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>11</v>
@@ -2643,11 +2650,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N11" s="43">
+      <c r="N11" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O11" s="43">
+      <c r="O11" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -2677,7 +2684,7 @@
       <c r="W11" s="11">
         <v>1.21E-2</v>
       </c>
-      <c r="X11" s="46">
+      <c r="X11" s="37">
         <f t="shared" si="4"/>
         <v>1.21</v>
       </c>
@@ -2688,11 +2695,11 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="45" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -2708,7 +2715,7 @@
         <v>264</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>37</v>
@@ -2722,10 +2729,10 @@
       <c r="M12" s="5">
         <v>30</v>
       </c>
-      <c r="N12" s="43">
+      <c r="N12" s="34">
         <v>130</v>
       </c>
-      <c r="O12" s="43">
+      <c r="O12" s="34">
         <v>520</v>
       </c>
       <c r="P12" s="14" t="s">
@@ -2748,14 +2755,14 @@
       <c r="U12" s="11">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="V12" s="46">
+      <c r="V12" s="37">
         <f t="shared" si="3"/>
         <v>3.835</v>
       </c>
       <c r="W12" s="11">
         <v>2.7699999999999999E-2</v>
       </c>
-      <c r="X12" s="46">
+      <c r="X12" s="37">
         <f t="shared" si="4"/>
         <v>14.404</v>
       </c>
@@ -2766,11 +2773,11 @@
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="B13" s="33"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="45" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="8" t="s">
@@ -2786,7 +2793,7 @@
         <v>265</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>41</v>
@@ -2801,10 +2808,10 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N13" s="43">
+      <c r="N13" s="34">
         <v>60</v>
       </c>
-      <c r="O13" s="43">
+      <c r="O13" s="34">
         <v>220</v>
       </c>
       <c r="P13" s="14" t="s">
@@ -2827,14 +2834,14 @@
       <c r="U13" s="11">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="V13" s="46">
+      <c r="V13" s="37">
         <f t="shared" si="3"/>
         <v>1.554</v>
       </c>
       <c r="W13" s="11">
         <v>1.8599999999999998E-2</v>
       </c>
-      <c r="X13" s="46">
+      <c r="X13" s="37">
         <f t="shared" si="4"/>
         <v>4.0919999999999996</v>
       </c>
@@ -2845,11 +2852,11 @@
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="B14" s="33"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="45" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="8" t="s">
@@ -2865,10 +2872,10 @@
         <v>266</v>
       </c>
       <c r="I14" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>323</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>324</v>
       </c>
       <c r="K14" s="8">
         <v>50</v>
@@ -2880,10 +2887,10 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N14" s="43">
+      <c r="N14" s="34">
         <v>100</v>
       </c>
-      <c r="O14" s="43">
+      <c r="O14" s="34">
         <v>250</v>
       </c>
       <c r="P14" s="14" t="s">
@@ -2906,14 +2913,14 @@
       <c r="U14" s="11">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="V14" s="46">
+      <c r="V14" s="37">
         <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
       <c r="W14" s="11">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="X14" s="46">
+      <c r="X14" s="37">
         <f t="shared" si="4"/>
         <v>1.875</v>
       </c>
@@ -2924,11 +2931,11 @@
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="B15" s="33"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="45" t="s">
         <v>248</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -2959,10 +2966,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N15" s="43">
+      <c r="N15" s="34">
         <v>120</v>
       </c>
-      <c r="O15" s="43">
+      <c r="O15" s="34">
         <v>420</v>
       </c>
       <c r="P15" s="14" t="s">
@@ -2985,14 +2992,14 @@
       <c r="U15" s="11">
         <v>1.9300000000000001E-2</v>
       </c>
-      <c r="V15" s="46">
+      <c r="V15" s="37">
         <f t="shared" si="3"/>
         <v>2.3160000000000003</v>
       </c>
       <c r="W15" s="11">
         <v>1.44E-2</v>
       </c>
-      <c r="X15" s="46">
+      <c r="X15" s="37">
         <f t="shared" si="4"/>
         <v>6.048</v>
       </c>
@@ -3003,11 +3010,11 @@
         <f>A15+1</f>
         <v>14</v>
       </c>
-      <c r="B16" s="33"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="46" t="s">
         <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -3023,7 +3030,7 @@
         <v>269</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>48</v>
@@ -3038,10 +3045,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N16" s="43">
+      <c r="N16" s="34">
         <v>110</v>
       </c>
-      <c r="O16" s="43">
+      <c r="O16" s="34">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
@@ -3065,14 +3072,14 @@
       <c r="U16" s="11">
         <v>3.5400000000000001E-2</v>
       </c>
-      <c r="V16" s="46">
+      <c r="V16" s="37">
         <f t="shared" si="3"/>
         <v>3.8940000000000001</v>
       </c>
       <c r="W16" s="11">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="X16" s="46">
+      <c r="X16" s="37">
         <f t="shared" si="4"/>
         <v>13.16</v>
       </c>
@@ -3083,11 +3090,11 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="B17" s="33"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="45" t="s">
         <v>51</v>
       </c>
       <c r="E17" s="8" t="s">
@@ -3100,10 +3107,10 @@
         <v>233</v>
       </c>
       <c r="H17" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="I17" s="19" t="s">
         <v>326</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>327</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>49</v>
@@ -3118,11 +3125,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N17" s="43">
+      <c r="N17" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O17" s="43">
+      <c r="O17" s="34">
         <v>150</v>
       </c>
       <c r="P17" s="14" t="s">
@@ -3144,13 +3151,13 @@
       <c r="U17" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="V17" s="46">
+      <c r="V17" s="37">
         <v>0.25</v>
       </c>
       <c r="W17" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="X17" s="46">
+      <c r="X17" s="37">
         <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
@@ -3161,11 +3168,11 @@
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="B18" s="33"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="45" t="s">
         <v>54</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -3181,7 +3188,7 @@
         <v>261</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>53</v>
@@ -3196,10 +3203,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N18" s="43">
+      <c r="N18" s="34">
         <v>40</v>
       </c>
-      <c r="O18" s="43">
+      <c r="O18" s="34">
         <v>120</v>
       </c>
       <c r="P18" s="14" t="s">
@@ -3222,14 +3229,14 @@
       <c r="U18" s="11">
         <v>3.1199999999999999E-2</v>
       </c>
-      <c r="V18" s="46">
+      <c r="V18" s="37">
         <f t="shared" si="3"/>
         <v>1.248</v>
       </c>
       <c r="W18" s="11">
         <v>3.1199999999999999E-2</v>
       </c>
-      <c r="X18" s="46">
+      <c r="X18" s="37">
         <f t="shared" si="4"/>
         <v>3.7439999999999998</v>
       </c>
@@ -3240,13 +3247,13 @@
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="60" t="s">
         <v>214</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="45" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -3261,8 +3268,8 @@
       <c r="H19" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="I19" s="60" t="s">
-        <v>323</v>
+      <c r="I19" s="51" t="s">
+        <v>322</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>55</v>
@@ -3277,10 +3284,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N19" s="43">
+      <c r="N19" s="34">
         <v>150</v>
       </c>
-      <c r="O19" s="43">
+      <c r="O19" s="34">
         <v>450</v>
       </c>
       <c r="P19" s="14" t="s">
@@ -3303,14 +3310,14 @@
       <c r="U19" s="11">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="V19" s="46">
+      <c r="V19" s="37">
         <f t="shared" si="3"/>
         <v>0.70500000000000007</v>
       </c>
       <c r="W19" s="11">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="X19" s="46">
+      <c r="X19" s="37">
         <f t="shared" si="4"/>
         <v>2.1150000000000002</v>
       </c>
@@ -3321,23 +3328,23 @@
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="B20" s="35"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="58" t="s">
-        <v>310</v>
-      </c>
-      <c r="F20" s="58" t="s">
+      <c r="E20" s="49" t="s">
+        <v>309</v>
+      </c>
+      <c r="F20" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="58" t="s">
+      <c r="G20" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="H20" s="58" t="s">
+      <c r="H20" s="49" t="s">
         <v>274</v>
       </c>
       <c r="I20" s="21"/>
@@ -3352,11 +3359,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N20" s="43">
+      <c r="N20" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O20" s="43">
+      <c r="O20" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -3378,12 +3385,12 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="U20" s="11"/>
-      <c r="V20" s="46">
+      <c r="V20" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W20" s="11"/>
-      <c r="X20" s="46">
+      <c r="X20" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3394,20 +3401,20 @@
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="58" t="s">
+      <c r="B21" s="61"/>
+      <c r="C21" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="58"/>
+      <c r="G21" s="49"/>
       <c r="H21" s="8"/>
       <c r="I21" s="21"/>
       <c r="J21" s="8"/>
@@ -3421,11 +3428,11 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N21" s="43">
+      <c r="N21" s="34">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="O21" s="43">
+      <c r="O21" s="34">
         <f t="shared" si="2"/>
         <v>800</v>
       </c>
@@ -3447,12 +3454,12 @@
         <v>10.664999999999999</v>
       </c>
       <c r="U21" s="11"/>
-      <c r="V21" s="46">
+      <c r="V21" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W21" s="11"/>
-      <c r="X21" s="46">
+      <c r="X21" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3463,15 +3470,15 @@
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="B22" s="35"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="45" t="s">
         <v>87</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>85</v>
@@ -3482,11 +3489,11 @@
       <c r="H22" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="I22" s="60" t="s">
+      <c r="I22" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>328</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>329</v>
       </c>
       <c r="K22" s="8">
         <v>5</v>
@@ -3498,10 +3505,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N22" s="43">
+      <c r="N22" s="34">
         <v>30</v>
       </c>
-      <c r="O22" s="43">
+      <c r="O22" s="34">
         <v>120</v>
       </c>
       <c r="P22" s="14" t="s">
@@ -3524,14 +3531,14 @@
       <c r="U22" s="11">
         <v>0.1326</v>
       </c>
-      <c r="V22" s="46">
+      <c r="V22" s="37">
         <f t="shared" si="3"/>
         <v>3.9779999999999998</v>
       </c>
       <c r="W22" s="11">
         <v>0.1011</v>
       </c>
-      <c r="X22" s="46">
+      <c r="X22" s="37">
         <f t="shared" si="4"/>
         <v>12.132</v>
       </c>
@@ -3542,11 +3549,11 @@
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="B23" s="36"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="D23" s="45" t="s">
         <v>90</v>
       </c>
       <c r="E23" s="8" t="s">
@@ -3555,8 +3562,8 @@
       <c r="F23" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="61" t="s">
-        <v>330</v>
+      <c r="G23" s="52" t="s">
+        <v>329</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>277</v>
@@ -3565,7 +3572,7 @@
         <v>276</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K23" s="8">
         <v>10</v>
@@ -3577,10 +3584,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N23" s="43">
+      <c r="N23" s="34">
         <v>30</v>
       </c>
-      <c r="O23" s="43">
+      <c r="O23" s="34">
         <v>120</v>
       </c>
       <c r="P23" s="14" t="s">
@@ -3603,14 +3610,14 @@
       <c r="U23" s="11">
         <v>7.3099999999999998E-2</v>
       </c>
-      <c r="V23" s="46">
+      <c r="V23" s="37">
         <f t="shared" si="3"/>
         <v>2.1930000000000001</v>
       </c>
       <c r="W23" s="11">
         <v>5.6800000000000003E-2</v>
       </c>
-      <c r="X23" s="46">
+      <c r="X23" s="37">
         <f t="shared" si="4"/>
         <v>6.8160000000000007</v>
       </c>
@@ -3629,11 +3636,11 @@
       <c r="C24" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="45" t="s">
         <v>69</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>67</v>
@@ -3645,10 +3652,10 @@
         <v>282</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K24" s="8">
         <v>1</v>
@@ -3660,11 +3667,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N24" s="43">
+      <c r="N24" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O24" s="43">
+      <c r="O24" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -3686,12 +3693,12 @@
         <v>0.745</v>
       </c>
       <c r="U24" s="11"/>
-      <c r="V24" s="46">
+      <c r="V24" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W24" s="11"/>
-      <c r="X24" s="46">
+      <c r="X24" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3708,11 +3715,11 @@
       <c r="C25" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="54" t="s">
+      <c r="D25" s="45" t="s">
         <v>84</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>82</v>
@@ -3722,7 +3729,7 @@
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K25" s="8">
         <v>1</v>
@@ -3734,11 +3741,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N25" s="43">
+      <c r="N25" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O25" s="43">
+      <c r="O25" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -3760,12 +3767,12 @@
         <v>3.9855</v>
       </c>
       <c r="U25" s="11"/>
-      <c r="V25" s="46">
+      <c r="V25" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W25" s="11"/>
-      <c r="X25" s="46">
+      <c r="X25" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3782,7 +3789,7 @@
       <c r="C26" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="54" t="s">
+      <c r="D26" s="45" t="s">
         <v>104</v>
       </c>
       <c r="E26" s="8" t="s">
@@ -3797,7 +3804,7 @@
       </c>
       <c r="I26" s="8"/>
       <c r="J26" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K26" s="8">
         <v>1</v>
@@ -3809,11 +3816,11 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N26" s="43">
+      <c r="N26" s="34">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="O26" s="43">
+      <c r="O26" s="34">
         <f t="shared" si="2"/>
         <v>800</v>
       </c>
@@ -3835,12 +3842,12 @@
         <v>99.108000000000004</v>
       </c>
       <c r="U26" s="11"/>
-      <c r="V26" s="46">
-        <f t="shared" si="3"/>
+      <c r="V26" s="37">
+        <f>U26*N26</f>
         <v>0</v>
       </c>
       <c r="W26" s="11"/>
-      <c r="X26" s="46">
+      <c r="X26" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3851,13 +3858,13 @@
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="60" t="s">
         <v>218</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="54" t="s">
+      <c r="D27" s="45" t="s">
         <v>108</v>
       </c>
       <c r="E27" s="8" t="s">
@@ -3884,11 +3891,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N27" s="43">
+      <c r="N27" s="34">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="O27" s="43">
+      <c r="O27" s="34">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
@@ -3910,12 +3917,12 @@
         <v>0.16999999999999998</v>
       </c>
       <c r="U27" s="11"/>
-      <c r="V27" s="46">
+      <c r="V27" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W27" s="11"/>
-      <c r="X27" s="46">
+      <c r="X27" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3926,11 +3933,11 @@
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="B28" s="35"/>
+      <c r="B28" s="61"/>
       <c r="C28" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="54" t="s">
+      <c r="D28" s="45" t="s">
         <v>112</v>
       </c>
       <c r="E28" s="8" t="s">
@@ -3959,11 +3966,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N28" s="43">
+      <c r="N28" s="34">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="O28" s="43">
+      <c r="O28" s="34">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
@@ -3985,12 +3992,12 @@
         <v>0.16999999999999998</v>
       </c>
       <c r="U28" s="11"/>
-      <c r="V28" s="46">
+      <c r="V28" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W28" s="11"/>
-      <c r="X28" s="46">
+      <c r="X28" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4001,11 +4008,11 @@
         <f t="shared" si="5"/>
         <v>27</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="61"/>
       <c r="C29" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="54" t="s">
+      <c r="D29" s="45" t="s">
         <v>116</v>
       </c>
       <c r="E29" s="8" t="s">
@@ -4034,11 +4041,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N29" s="43">
+      <c r="N29" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O29" s="43">
+      <c r="O29" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4060,12 +4067,12 @@
         <v>0.21</v>
       </c>
       <c r="U29" s="11"/>
-      <c r="V29" s="46">
+      <c r="V29" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W29" s="11"/>
-      <c r="X29" s="46">
+      <c r="X29" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4076,11 +4083,11 @@
         <f t="shared" si="5"/>
         <v>28</v>
       </c>
-      <c r="B30" s="35"/>
+      <c r="B30" s="61"/>
       <c r="C30" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="54" t="s">
+      <c r="D30" s="45" t="s">
         <v>120</v>
       </c>
       <c r="E30" s="8" t="s">
@@ -4109,11 +4116,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N30" s="43">
+      <c r="N30" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O30" s="43">
+      <c r="O30" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4135,12 +4142,12 @@
         <v>0.13999999999999999</v>
       </c>
       <c r="U30" s="11"/>
-      <c r="V30" s="46">
+      <c r="V30" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W30" s="11"/>
-      <c r="X30" s="46">
+      <c r="X30" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4151,11 +4158,11 @@
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="61"/>
       <c r="C31" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="45" t="s">
         <v>124</v>
       </c>
       <c r="E31" s="8" t="s">
@@ -4184,11 +4191,11 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N31" s="43">
+      <c r="N31" s="34">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="O31" s="43">
+      <c r="O31" s="34">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
@@ -4210,12 +4217,12 @@
         <v>0.22999999999999998</v>
       </c>
       <c r="U31" s="11"/>
-      <c r="V31" s="46">
+      <c r="V31" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W31" s="11"/>
-      <c r="X31" s="46">
+      <c r="X31" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4226,11 +4233,11 @@
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="B32" s="35"/>
+      <c r="B32" s="61"/>
       <c r="C32" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="D32" s="45" t="s">
         <v>128</v>
       </c>
       <c r="E32" s="8" t="s">
@@ -4259,11 +4266,11 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N32" s="43">
+      <c r="N32" s="34">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="O32" s="43">
+      <c r="O32" s="34">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
@@ -4285,12 +4292,12 @@
         <v>1.714</v>
       </c>
       <c r="U32" s="11"/>
-      <c r="V32" s="46">
+      <c r="V32" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W32" s="11"/>
-      <c r="X32" s="46">
+      <c r="X32" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4301,11 +4308,11 @@
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="61"/>
       <c r="C33" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="54" t="s">
+      <c r="D33" s="45" t="s">
         <v>133</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -4334,11 +4341,11 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N33" s="43">
+      <c r="N33" s="34">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="O33" s="43">
+      <c r="O33" s="34">
         <f t="shared" si="2"/>
         <v>800</v>
       </c>
@@ -4360,12 +4367,12 @@
         <v>0.22</v>
       </c>
       <c r="U33" s="11"/>
-      <c r="V33" s="46">
+      <c r="V33" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W33" s="11"/>
-      <c r="X33" s="46">
+      <c r="X33" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4376,11 +4383,11 @@
         <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="B34" s="35"/>
+      <c r="B34" s="61"/>
       <c r="C34" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="54" t="s">
+      <c r="D34" s="45" t="s">
         <v>137</v>
       </c>
       <c r="E34" s="8" t="s">
@@ -4409,11 +4416,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N34" s="43">
+      <c r="N34" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O34" s="43">
+      <c r="O34" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4435,12 +4442,12 @@
         <v>0.46499999999999997</v>
       </c>
       <c r="U34" s="11"/>
-      <c r="V34" s="46">
+      <c r="V34" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W34" s="11"/>
-      <c r="X34" s="46">
+      <c r="X34" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4451,11 +4458,11 @@
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="61"/>
       <c r="C35" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="45" t="s">
         <v>141</v>
       </c>
       <c r="E35" s="8" t="s">
@@ -4484,11 +4491,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N35" s="43">
+      <c r="N35" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O35" s="43">
+      <c r="O35" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4510,12 +4517,12 @@
         <v>0.2</v>
       </c>
       <c r="U35" s="11"/>
-      <c r="V35" s="46">
+      <c r="V35" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W35" s="11"/>
-      <c r="X35" s="46">
+      <c r="X35" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4526,11 +4533,11 @@
         <f t="shared" si="5"/>
         <v>34</v>
       </c>
-      <c r="B36" s="35"/>
+      <c r="B36" s="61"/>
       <c r="C36" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="D36" s="45" t="s">
         <v>145</v>
       </c>
       <c r="E36" s="8" t="s">
@@ -4559,11 +4566,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N36" s="43">
+      <c r="N36" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O36" s="43">
+      <c r="O36" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4585,12 +4592,12 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="U36" s="11"/>
-      <c r="V36" s="46">
+      <c r="V36" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W36" s="11"/>
-      <c r="X36" s="46">
+      <c r="X36" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4601,11 +4608,11 @@
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="B37" s="35"/>
+      <c r="B37" s="61"/>
       <c r="C37" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D37" s="54" t="s">
+      <c r="D37" s="45" t="s">
         <v>149</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -4634,11 +4641,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N37" s="43">
+      <c r="N37" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O37" s="43">
+      <c r="O37" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4660,12 +4667,12 @@
         <v>0.21</v>
       </c>
       <c r="U37" s="11"/>
-      <c r="V37" s="46">
+      <c r="V37" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W37" s="11"/>
-      <c r="X37" s="46">
+      <c r="X37" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4676,11 +4683,11 @@
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="B38" s="35"/>
+      <c r="B38" s="61"/>
       <c r="C38" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D38" s="54" t="s">
+      <c r="D38" s="45" t="s">
         <v>153</v>
       </c>
       <c r="E38" s="8" t="s">
@@ -4709,11 +4716,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N38" s="43">
+      <c r="N38" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O38" s="43">
+      <c r="O38" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4735,12 +4742,12 @@
         <v>0.92999999999999994</v>
       </c>
       <c r="U38" s="11"/>
-      <c r="V38" s="46">
+      <c r="V38" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W38" s="11"/>
-      <c r="X38" s="46">
+      <c r="X38" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4751,11 +4758,11 @@
         <f t="shared" si="5"/>
         <v>37</v>
       </c>
-      <c r="B39" s="35"/>
+      <c r="B39" s="61"/>
       <c r="C39" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="54" t="s">
+      <c r="D39" s="45" t="s">
         <v>157</v>
       </c>
       <c r="E39" s="8" t="s">
@@ -4784,11 +4791,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N39" s="43">
+      <c r="N39" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O39" s="43">
+      <c r="O39" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4810,12 +4817,12 @@
         <v>0.26</v>
       </c>
       <c r="U39" s="11"/>
-      <c r="V39" s="46">
+      <c r="V39" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W39" s="11"/>
-      <c r="X39" s="46">
+      <c r="X39" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4826,11 +4833,11 @@
         <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="B40" s="36"/>
+      <c r="B40" s="58"/>
       <c r="C40" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D40" s="54" t="s">
+      <c r="D40" s="45" t="s">
         <v>161</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -4859,11 +4866,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N40" s="43">
+      <c r="N40" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O40" s="43">
+      <c r="O40" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4885,12 +4892,12 @@
         <v>0.2</v>
       </c>
       <c r="U40" s="11"/>
-      <c r="V40" s="46">
+      <c r="V40" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W40" s="11"/>
-      <c r="X40" s="46">
+      <c r="X40" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4901,17 +4908,17 @@
         <f t="shared" si="5"/>
         <v>39</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B41" s="60" t="s">
         <v>219</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D41" s="54" t="s">
+      <c r="D41" s="45" t="s">
         <v>168</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>166</v>
@@ -4930,11 +4937,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N41" s="43">
+      <c r="N41" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O41" s="43">
+      <c r="O41" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4955,12 +4962,12 @@
         <v>1.8</v>
       </c>
       <c r="U41" s="11"/>
-      <c r="V41" s="46">
+      <c r="V41" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W41" s="11"/>
-      <c r="X41" s="46">
+      <c r="X41" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4971,15 +4978,15 @@
         <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="B42" s="36"/>
+      <c r="B42" s="58"/>
       <c r="C42" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D42" s="54" t="s">
+      <c r="D42" s="45" t="s">
         <v>171</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>169</v>
@@ -5002,11 +5009,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N42" s="43">
+      <c r="N42" s="34">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="O42" s="43">
+      <c r="O42" s="34">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
@@ -5028,12 +5035,12 @@
         <v>2.093</v>
       </c>
       <c r="U42" s="11"/>
-      <c r="V42" s="46">
+      <c r="V42" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W42" s="11"/>
-      <c r="X42" s="46">
+      <c r="X42" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5044,13 +5051,13 @@
         <f t="shared" si="5"/>
         <v>41</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="60" t="s">
         <v>220</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="54" t="s">
+      <c r="D43" s="45" t="s">
         <v>174</v>
       </c>
       <c r="E43" s="8" t="s">
@@ -5077,11 +5084,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N43" s="43">
+      <c r="N43" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O43" s="43">
+      <c r="O43" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5102,13 +5109,13 @@
         <f t="shared" si="6"/>
         <v>0.9365</v>
       </c>
-      <c r="U43" s="56"/>
-      <c r="V43" s="46">
+      <c r="U43" s="47"/>
+      <c r="V43" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W43" s="56"/>
-      <c r="X43" s="46">
+      <c r="W43" s="47"/>
+      <c r="X43" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5118,11 +5125,11 @@
         <f t="shared" si="5"/>
         <v>42</v>
       </c>
-      <c r="B44" s="35"/>
+      <c r="B44" s="61"/>
       <c r="C44" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D44" s="54" t="s">
+      <c r="D44" s="45" t="s">
         <v>178</v>
       </c>
       <c r="E44" s="8" t="s">
@@ -5149,11 +5156,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N44" s="43">
+      <c r="N44" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O44" s="43">
+      <c r="O44" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5175,12 +5182,12 @@
         <v>1.7389999999999999</v>
       </c>
       <c r="U44" s="11"/>
-      <c r="V44" s="46">
+      <c r="V44" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W44" s="11"/>
-      <c r="X44" s="46">
+      <c r="X44" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5191,11 +5198,11 @@
         <f t="shared" si="5"/>
         <v>43</v>
       </c>
-      <c r="B45" s="35"/>
+      <c r="B45" s="61"/>
       <c r="C45" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D45" s="45" t="s">
         <v>182</v>
       </c>
       <c r="E45" s="8" t="s">
@@ -5222,11 +5229,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N45" s="43">
+      <c r="N45" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O45" s="43">
+      <c r="O45" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5248,12 +5255,12 @@
         <v>7.9615</v>
       </c>
       <c r="U45" s="11"/>
-      <c r="V45" s="46">
+      <c r="V45" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W45" s="11"/>
-      <c r="X45" s="46">
+      <c r="X45" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5264,11 +5271,11 @@
         <f t="shared" si="5"/>
         <v>44</v>
       </c>
-      <c r="B46" s="35"/>
+      <c r="B46" s="61"/>
       <c r="C46" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D46" s="54" t="s">
+      <c r="D46" s="45" t="s">
         <v>186</v>
       </c>
       <c r="E46" s="8" t="s">
@@ -5293,11 +5300,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N46" s="43">
+      <c r="N46" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O46" s="43">
+      <c r="O46" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5319,12 +5326,12 @@
         <v>1.732</v>
       </c>
       <c r="U46" s="11"/>
-      <c r="V46" s="46">
+      <c r="V46" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W46" s="11"/>
-      <c r="X46" s="46">
+      <c r="X46" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5335,11 +5342,11 @@
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="B47" s="35"/>
+      <c r="B47" s="61"/>
       <c r="C47" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D47" s="54" t="s">
+      <c r="D47" s="45" t="s">
         <v>190</v>
       </c>
       <c r="E47" s="8" t="s">
@@ -5366,11 +5373,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N47" s="43">
+      <c r="N47" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O47" s="43">
+      <c r="O47" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5392,12 +5399,12 @@
         <v>1.5310000000000001</v>
       </c>
       <c r="U47" s="11"/>
-      <c r="V47" s="46">
+      <c r="V47" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W47" s="11"/>
-      <c r="X47" s="46">
+      <c r="X47" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5408,11 +5415,11 @@
         <f t="shared" si="5"/>
         <v>46</v>
       </c>
-      <c r="B48" s="35"/>
+      <c r="B48" s="61"/>
       <c r="C48" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D48" s="54" t="s">
+      <c r="D48" s="45" t="s">
         <v>194</v>
       </c>
       <c r="E48" s="8" t="s">
@@ -5435,11 +5442,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N48" s="43">
+      <c r="N48" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O48" s="43">
+      <c r="O48" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5463,12 +5470,12 @@
         <v>37.049999999999997</v>
       </c>
       <c r="U48" s="11"/>
-      <c r="V48" s="46">
+      <c r="V48" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W48" s="11"/>
-      <c r="X48" s="46">
+      <c r="X48" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5479,11 +5486,11 @@
         <f t="shared" si="5"/>
         <v>47</v>
       </c>
-      <c r="B49" s="36"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D49" s="54" t="s">
+      <c r="D49" s="45" t="s">
         <v>198</v>
       </c>
       <c r="E49" s="8" t="s">
@@ -5508,11 +5515,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N49" s="43">
+      <c r="N49" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O49" s="43">
+      <c r="O49" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5534,12 +5541,12 @@
         <v>9.6</v>
       </c>
       <c r="U49" s="11"/>
-      <c r="V49" s="46">
+      <c r="V49" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W49" s="11"/>
-      <c r="X49" s="46">
+      <c r="X49" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5550,7 +5557,7 @@
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="53" t="s">
         <v>221</v>
       </c>
       <c r="C50" s="8" t="s">
@@ -5560,7 +5567,7 @@
         <v>72</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>70</v>
@@ -5583,11 +5590,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N50" s="43">
+      <c r="N50" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O50" s="43">
+      <c r="O50" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5609,12 +5616,12 @@
         <v>9.2240000000000002</v>
       </c>
       <c r="U50" s="11"/>
-      <c r="V50" s="46">
+      <c r="V50" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W50" s="11"/>
-      <c r="X50" s="46">
+      <c r="X50" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5625,7 +5632,7 @@
         <f t="shared" si="5"/>
         <v>49</v>
       </c>
-      <c r="B51" s="38"/>
+      <c r="B51" s="54"/>
       <c r="C51" s="8" t="s">
         <v>74</v>
       </c>
@@ -5633,7 +5640,7 @@
         <v>75</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>73</v>
@@ -5656,11 +5663,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N51" s="43">
+      <c r="N51" s="34">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="O51" s="43">
+      <c r="O51" s="34">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
@@ -5682,23 +5689,23 @@
         <v>7.2860000000000005</v>
       </c>
       <c r="U51" s="11"/>
-      <c r="V51" s="46">
+      <c r="V51" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W51" s="11"/>
-      <c r="X51" s="46">
+      <c r="X51" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y51" s="5"/>
     </row>
-    <row r="52" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="B52" s="38"/>
+      <c r="B52" s="54"/>
       <c r="C52" s="8" t="s">
         <v>77</v>
       </c>
@@ -5706,7 +5713,7 @@
         <v>78</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>76</v>
@@ -5727,43 +5734,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N52" s="43">
+      <c r="N52" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O52" s="43">
+      <c r="O52" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q52" s="10">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R52" s="11">
         <f t="shared" si="7"/>
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="S52" s="10">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="T52" s="11">
         <f t="shared" si="6"/>
-        <v>8.6999999999999993</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="U52" s="11"/>
-      <c r="V52" s="46">
+      <c r="V52" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W52" s="11"/>
-      <c r="X52" s="46">
+      <c r="X52" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y52" s="5" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
@@ -5771,7 +5778,7 @@
         <f t="shared" si="5"/>
         <v>51</v>
       </c>
-      <c r="B53" s="38"/>
+      <c r="B53" s="54"/>
       <c r="C53" s="8" t="s">
         <v>80</v>
       </c>
@@ -5779,7 +5786,7 @@
         <v>81</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>79</v>
@@ -5800,11 +5807,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N53" s="43">
+      <c r="N53" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O53" s="43">
+      <c r="O53" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -5825,12 +5832,12 @@
         <v>4</v>
       </c>
       <c r="U53" s="11"/>
-      <c r="V53" s="46">
+      <c r="V53" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W53" s="11"/>
-      <c r="X53" s="46">
+      <c r="X53" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5841,7 +5848,7 @@
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="B54" s="38"/>
+      <c r="B54" s="54"/>
       <c r="C54" s="8" t="s">
         <v>93</v>
       </c>
@@ -5849,7 +5856,7 @@
         <v>94</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>92</v>
@@ -5870,11 +5877,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N54" s="43">
+      <c r="N54" s="34">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="O54" s="43">
+      <c r="O54" s="34">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
@@ -5896,12 +5903,12 @@
         <v>16.100000000000001</v>
       </c>
       <c r="U54" s="11"/>
-      <c r="V54" s="46">
+      <c r="V54" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W54" s="11"/>
-      <c r="X54" s="46">
+      <c r="X54" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5912,7 +5919,7 @@
         <f t="shared" si="5"/>
         <v>53</v>
       </c>
-      <c r="B55" s="38"/>
+      <c r="B55" s="54"/>
       <c r="C55" s="8" t="s">
         <v>98</v>
       </c>
@@ -5941,11 +5948,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N55" s="43">
+      <c r="N55" s="34">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="O55" s="43">
+      <c r="O55" s="34">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
@@ -5964,13 +5971,13 @@
       <c r="T55" s="10">
         <v>0.19</v>
       </c>
-      <c r="U55" s="57"/>
-      <c r="V55" s="46">
+      <c r="U55" s="48"/>
+      <c r="V55" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W55" s="57"/>
-      <c r="X55" s="46">
+      <c r="W55" s="48"/>
+      <c r="X55" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -5980,7 +5987,7 @@
         <f t="shared" si="5"/>
         <v>54</v>
       </c>
-      <c r="B56" s="38"/>
+      <c r="B56" s="54"/>
       <c r="C56" s="15" t="s">
         <v>95</v>
       </c>
@@ -6005,11 +6012,11 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N56" s="43">
+      <c r="N56" s="34">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="O56" s="43">
+      <c r="O56" s="34">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
@@ -6041,7 +6048,7 @@
         <f t="shared" si="5"/>
         <v>55</v>
       </c>
-      <c r="B57" s="38"/>
+      <c r="B57" s="54"/>
       <c r="C57" s="15" t="s">
         <v>164</v>
       </c>
@@ -6066,11 +6073,11 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N57" s="43">
+      <c r="N57" s="34">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="O57" s="43">
+      <c r="O57" s="34">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -6117,12 +6124,12 @@
       <c r="Q58" s="24"/>
       <c r="R58" s="25">
         <f>SUM(R3:R55)</f>
-        <v>73.678699999999992</v>
+        <v>73.628699999999995</v>
       </c>
       <c r="S58" s="23"/>
       <c r="T58" s="26">
         <f>SUM(T3:T55)</f>
-        <v>248.25999999999993</v>
+        <v>248.00999999999993</v>
       </c>
       <c r="U58" s="26"/>
       <c r="V58" s="26"/>
